--- a/ulmtool2.xlsx
+++ b/ulmtool2.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="\\bauanalytix\home\07_Bauanalytix 2026\2026041 Beratung VuB Hochbau\2026041-5 Online-Tools Versuchsstadium\Github UlmTool_Version 2\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{F5B739CB-BBA2-4A48-A9A4-FDAC89D38614}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{699D13CA-7248-44EA-89E9-A6566E45B37A}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-90" yWindow="-90" windowWidth="19380" windowHeight="10260" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -41,7 +41,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="7977" uniqueCount="997">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="7977" uniqueCount="996">
   <si>
     <t>PAK</t>
   </si>
@@ -3213,9 +3213,6 @@
     <t>Deckenkörper</t>
   </si>
   <si>
-    <t>keine Information</t>
-  </si>
-  <si>
     <t>Hinweise</t>
   </si>
   <si>
@@ -3270,16 +3267,16 @@
     <t>Handlungshinweise</t>
   </si>
   <si>
-    <t>https://bauanalytix.github.io/Uni-Ulm-Handlungshinweise-Wilhelmi/ mit Kantenprofil</t>
-  </si>
-  <si>
     <t>https://bauanalytix.github.io/Uni-Ulm-Handlungshinweise-Wilhelmi/</t>
   </si>
   <si>
-    <t>https://bauanalytix.github.io/Uni-Ulm-Handlungshinweise-Wilhelmi/-Deckenplatten</t>
-  </si>
-  <si>
     <t>https://bauanalytix.github.io/Uni-Ulm-Handlungshinweise-KMFallg/</t>
+  </si>
+  <si>
+    <t>Wilhelmi-Deckenplatten</t>
+  </si>
+  <si>
+    <t>unbekannt</t>
   </si>
 </sst>
 </file>
@@ -4226,7 +4223,7 @@
         <v>533</v>
       </c>
       <c r="E1" s="61" t="s">
-        <v>979</v>
+        <v>978</v>
       </c>
       <c r="F1" s="61" t="s">
         <v>1</v>
@@ -4262,7 +4259,7 @@
         <v>968</v>
       </c>
       <c r="Q1" s="3" t="s">
-        <v>992</v>
+        <v>991</v>
       </c>
     </row>
     <row r="2" spans="1:17" s="9" customFormat="1" ht="27" customHeight="1" x14ac:dyDescent="0.75">
@@ -4279,7 +4276,7 @@
         <v>17</v>
       </c>
       <c r="E2" s="7" t="s">
-        <v>989</v>
+        <v>988</v>
       </c>
       <c r="F2" s="7" t="s">
         <v>18</v>
@@ -4321,7 +4318,7 @@
         <v>17</v>
       </c>
       <c r="E3" s="7" t="s">
-        <v>989</v>
+        <v>988</v>
       </c>
       <c r="F3" s="7" t="s">
         <v>22</v>
@@ -4363,7 +4360,7 @@
         <v>17</v>
       </c>
       <c r="E4" s="7" t="s">
-        <v>989</v>
+        <v>988</v>
       </c>
       <c r="F4" s="7" t="s">
         <v>25</v>
@@ -4405,7 +4402,7 @@
         <v>17</v>
       </c>
       <c r="E5" s="7" t="s">
-        <v>984</v>
+        <v>983</v>
       </c>
       <c r="F5" s="7" t="s">
         <v>27</v>
@@ -4447,7 +4444,7 @@
         <v>17</v>
       </c>
       <c r="E6" s="7" t="s">
-        <v>984</v>
+        <v>983</v>
       </c>
       <c r="F6" s="7" t="s">
         <v>30</v>
@@ -4489,7 +4486,7 @@
         <v>17</v>
       </c>
       <c r="E7" s="7" t="s">
-        <v>981</v>
+        <v>980</v>
       </c>
       <c r="F7" s="7" t="s">
         <v>32</v>
@@ -4531,7 +4528,7 @@
         <v>352</v>
       </c>
       <c r="E8" s="7" t="s">
-        <v>984</v>
+        <v>983</v>
       </c>
       <c r="F8" s="17" t="s">
         <v>34</v>
@@ -4573,7 +4570,7 @@
         <v>352</v>
       </c>
       <c r="E9" s="7" t="s">
-        <v>981</v>
+        <v>980</v>
       </c>
       <c r="F9" s="17" t="s">
         <v>37</v>
@@ -4615,7 +4612,7 @@
         <v>40</v>
       </c>
       <c r="E10" s="7" t="s">
-        <v>981</v>
+        <v>980</v>
       </c>
       <c r="F10" s="17" t="s">
         <v>41</v>
@@ -4657,7 +4654,7 @@
         <v>44</v>
       </c>
       <c r="E11" s="7" t="s">
-        <v>984</v>
+        <v>983</v>
       </c>
       <c r="F11" s="17" t="s">
         <v>45</v>
@@ -4699,7 +4696,7 @@
         <v>47</v>
       </c>
       <c r="E12" s="7" t="s">
-        <v>984</v>
+        <v>983</v>
       </c>
       <c r="F12" s="17" t="s">
         <v>358</v>
@@ -4741,7 +4738,7 @@
         <v>50</v>
       </c>
       <c r="E13" s="7" t="s">
-        <v>984</v>
+        <v>983</v>
       </c>
       <c r="F13" s="7" t="s">
         <v>51</v>
@@ -4783,7 +4780,7 @@
         <v>55</v>
       </c>
       <c r="E14" s="11" t="s">
-        <v>984</v>
+        <v>983</v>
       </c>
       <c r="F14" s="7" t="s">
         <v>56</v>
@@ -4825,7 +4822,7 @@
         <v>353</v>
       </c>
       <c r="E15" s="7" t="s">
-        <v>984</v>
+        <v>983</v>
       </c>
       <c r="F15" s="7" t="s">
         <v>58</v>
@@ -4867,7 +4864,7 @@
         <v>353</v>
       </c>
       <c r="E16" s="7" t="s">
-        <v>981</v>
+        <v>980</v>
       </c>
       <c r="F16" s="7" t="s">
         <v>61</v>
@@ -4909,7 +4906,7 @@
         <v>353</v>
       </c>
       <c r="E17" s="7" t="s">
-        <v>981</v>
+        <v>980</v>
       </c>
       <c r="F17" s="7" t="s">
         <v>64</v>
@@ -4951,7 +4948,7 @@
         <v>67</v>
       </c>
       <c r="E18" s="7" t="s">
-        <v>989</v>
+        <v>988</v>
       </c>
       <c r="F18" s="7" t="s">
         <v>68</v>
@@ -4993,7 +4990,7 @@
         <v>67</v>
       </c>
       <c r="E19" s="90" t="s">
-        <v>984</v>
+        <v>983</v>
       </c>
       <c r="F19" s="7" t="s">
         <v>70</v>
@@ -5115,7 +5112,7 @@
         <v>370</v>
       </c>
       <c r="E22" s="24" t="s">
-        <v>980</v>
+        <v>979</v>
       </c>
       <c r="F22" s="15" t="s">
         <v>13</v>
@@ -6449,7 +6446,7 @@
         <v>142</v>
       </c>
       <c r="E54" s="51" t="s">
-        <v>985</v>
+        <v>984</v>
       </c>
       <c r="F54" s="34" t="s">
         <v>143</v>
@@ -7091,7 +7088,7 @@
         <v>157</v>
       </c>
       <c r="E69" s="51" t="s">
-        <v>981</v>
+        <v>980</v>
       </c>
       <c r="F69" s="34" t="s">
         <v>160</v>
@@ -7217,7 +7214,7 @@
         <v>161</v>
       </c>
       <c r="E72" s="51" t="s">
-        <v>986</v>
+        <v>985</v>
       </c>
       <c r="F72" s="34" t="s">
         <v>163</v>
@@ -7259,7 +7256,7 @@
         <v>164</v>
       </c>
       <c r="E73" s="51" t="s">
-        <v>990</v>
+        <v>989</v>
       </c>
       <c r="F73" s="34" t="s">
         <v>165</v>
@@ -7301,7 +7298,7 @@
         <v>164</v>
       </c>
       <c r="E74" s="51" t="s">
-        <v>984</v>
+        <v>983</v>
       </c>
       <c r="F74" s="34" t="s">
         <v>166</v>
@@ -7343,7 +7340,7 @@
         <v>167</v>
       </c>
       <c r="E75" s="51" t="s">
-        <v>980</v>
+        <v>979</v>
       </c>
       <c r="F75" s="34" t="s">
         <v>168</v>
@@ -7385,7 +7382,7 @@
         <v>167</v>
       </c>
       <c r="E76" s="51" t="s">
-        <v>980</v>
+        <v>979</v>
       </c>
       <c r="F76" s="34" t="s">
         <v>169</v>
@@ -7427,7 +7424,7 @@
         <v>170</v>
       </c>
       <c r="E77" s="7" t="s">
-        <v>989</v>
+        <v>988</v>
       </c>
       <c r="F77" s="34" t="s">
         <v>171</v>
@@ -7469,7 +7466,7 @@
         <v>172</v>
       </c>
       <c r="E78" s="51" t="s">
-        <v>982</v>
+        <v>981</v>
       </c>
       <c r="F78" s="34" t="s">
         <v>173</v>
@@ -7637,7 +7634,7 @@
         <v>177</v>
       </c>
       <c r="E82" s="51" t="s">
-        <v>985</v>
+        <v>984</v>
       </c>
       <c r="F82" s="34" t="s">
         <v>178</v>
@@ -7681,7 +7678,7 @@
         <v>177</v>
       </c>
       <c r="E83" s="51" t="s">
-        <v>985</v>
+        <v>984</v>
       </c>
       <c r="F83" s="34" t="s">
         <v>178</v>
@@ -8563,7 +8560,7 @@
         <v>331</v>
       </c>
       <c r="E104" s="51" t="s">
-        <v>984</v>
+        <v>983</v>
       </c>
       <c r="F104" s="51" t="s">
         <v>332</v>
@@ -8607,7 +8604,7 @@
         <v>331</v>
       </c>
       <c r="E105" s="7" t="s">
-        <v>989</v>
+        <v>988</v>
       </c>
       <c r="F105" s="51" t="s">
         <v>333</v>
@@ -8649,7 +8646,7 @@
         <v>331</v>
       </c>
       <c r="E106" s="7" t="s">
-        <v>989</v>
+        <v>988</v>
       </c>
       <c r="F106" s="51" t="s">
         <v>335</v>
@@ -9113,7 +9110,7 @@
         <v>181</v>
       </c>
       <c r="E117" s="51" t="s">
-        <v>984</v>
+        <v>983</v>
       </c>
       <c r="F117" s="34" t="s">
         <v>201</v>
@@ -9155,7 +9152,7 @@
         <v>181</v>
       </c>
       <c r="E118" s="51" t="s">
-        <v>980</v>
+        <v>979</v>
       </c>
       <c r="F118" s="34" t="s">
         <v>202</v>
@@ -9197,7 +9194,7 @@
         <v>181</v>
       </c>
       <c r="E119" s="51" t="s">
-        <v>988</v>
+        <v>987</v>
       </c>
       <c r="F119" s="34" t="s">
         <v>203</v>
@@ -9239,7 +9236,7 @@
         <v>204</v>
       </c>
       <c r="E120" s="51" t="s">
-        <v>988</v>
+        <v>987</v>
       </c>
       <c r="F120" s="34" t="s">
         <v>205</v>
@@ -9323,7 +9320,7 @@
         <v>181</v>
       </c>
       <c r="E122" s="51" t="s">
-        <v>980</v>
+        <v>979</v>
       </c>
       <c r="F122" s="34" t="s">
         <v>207</v>
@@ -9449,7 +9446,7 @@
         <v>204</v>
       </c>
       <c r="E125" s="51" t="s">
-        <v>983</v>
+        <v>982</v>
       </c>
       <c r="F125" s="34" t="s">
         <v>209</v>
@@ -9491,7 +9488,7 @@
         <v>210</v>
       </c>
       <c r="E126" s="51" t="s">
-        <v>980</v>
+        <v>979</v>
       </c>
       <c r="F126" s="34" t="s">
         <v>211</v>
@@ -9701,7 +9698,7 @@
         <v>216</v>
       </c>
       <c r="E131" s="51" t="s">
-        <v>983</v>
+        <v>982</v>
       </c>
       <c r="F131" s="34" t="s">
         <v>217</v>
@@ -9743,7 +9740,7 @@
         <v>218</v>
       </c>
       <c r="E132" s="51" t="s">
-        <v>983</v>
+        <v>982</v>
       </c>
       <c r="F132" s="34" t="s">
         <v>219</v>
@@ -9785,7 +9782,7 @@
         <v>216</v>
       </c>
       <c r="E133" s="51" t="s">
-        <v>983</v>
+        <v>982</v>
       </c>
       <c r="F133" s="34" t="s">
         <v>217</v>
@@ -10421,7 +10418,7 @@
         <v>229</v>
       </c>
       <c r="E148" s="51" t="s">
-        <v>989</v>
+        <v>988</v>
       </c>
       <c r="F148" s="34" t="s">
         <v>230</v>
@@ -10505,7 +10502,7 @@
         <v>233</v>
       </c>
       <c r="E150" s="51" t="s">
-        <v>990</v>
+        <v>989</v>
       </c>
       <c r="F150" s="34" t="s">
         <v>234</v>
@@ -10549,7 +10546,7 @@
         <v>235</v>
       </c>
       <c r="E151" s="51" t="s">
-        <v>990</v>
+        <v>989</v>
       </c>
       <c r="F151" s="34" t="s">
         <v>236</v>
@@ -10591,7 +10588,7 @@
         <v>235</v>
       </c>
       <c r="E152" s="51" t="s">
-        <v>990</v>
+        <v>989</v>
       </c>
       <c r="F152" s="34" t="s">
         <v>237</v>
@@ -10633,7 +10630,7 @@
         <v>238</v>
       </c>
       <c r="E153" s="51" t="s">
-        <v>990</v>
+        <v>989</v>
       </c>
       <c r="F153" s="34" t="s">
         <v>239</v>
@@ -10675,7 +10672,7 @@
         <v>235</v>
       </c>
       <c r="E154" s="51" t="s">
-        <v>990</v>
+        <v>989</v>
       </c>
       <c r="F154" s="34" t="s">
         <v>240</v>
@@ -10717,7 +10714,7 @@
         <v>235</v>
       </c>
       <c r="E155" s="51" t="s">
-        <v>990</v>
+        <v>989</v>
       </c>
       <c r="F155" s="34" t="s">
         <v>241</v>
@@ -10759,7 +10756,7 @@
         <v>235</v>
       </c>
       <c r="E156" s="51" t="s">
-        <v>990</v>
+        <v>989</v>
       </c>
       <c r="F156" s="34" t="s">
         <v>241</v>
@@ -10801,7 +10798,7 @@
         <v>218</v>
       </c>
       <c r="E157" s="51" t="s">
-        <v>990</v>
+        <v>989</v>
       </c>
       <c r="F157" s="34" t="s">
         <v>242</v>
@@ -10843,7 +10840,7 @@
         <v>218</v>
       </c>
       <c r="E158" s="51" t="s">
-        <v>990</v>
+        <v>989</v>
       </c>
       <c r="F158" s="34" t="s">
         <v>243</v>
@@ -10885,7 +10882,7 @@
         <v>218</v>
       </c>
       <c r="E159" s="51" t="s">
-        <v>990</v>
+        <v>989</v>
       </c>
       <c r="F159" s="34" t="s">
         <v>243</v>
@@ -10927,7 +10924,7 @@
         <v>244</v>
       </c>
       <c r="E160" s="51" t="s">
-        <v>990</v>
+        <v>989</v>
       </c>
       <c r="F160" s="34" t="s">
         <v>245</v>
@@ -10969,7 +10966,7 @@
         <v>244</v>
       </c>
       <c r="E161" s="51" t="s">
-        <v>990</v>
+        <v>989</v>
       </c>
       <c r="F161" s="34" t="s">
         <v>246</v>
@@ -11011,7 +11008,7 @@
         <v>244</v>
       </c>
       <c r="E162" s="51" t="s">
-        <v>990</v>
+        <v>989</v>
       </c>
       <c r="F162" s="34" t="s">
         <v>246</v>
@@ -11053,7 +11050,7 @@
         <v>247</v>
       </c>
       <c r="E163" s="51" t="s">
-        <v>990</v>
+        <v>989</v>
       </c>
       <c r="F163" s="34" t="s">
         <v>248</v>
@@ -11095,7 +11092,7 @@
         <v>247</v>
       </c>
       <c r="E164" s="51" t="s">
-        <v>990</v>
+        <v>989</v>
       </c>
       <c r="F164" s="34" t="s">
         <v>249</v>
@@ -11137,7 +11134,7 @@
         <v>244</v>
       </c>
       <c r="E165" s="51" t="s">
-        <v>990</v>
+        <v>989</v>
       </c>
       <c r="F165" s="34" t="s">
         <v>250</v>
@@ -11179,7 +11176,7 @@
         <v>251</v>
       </c>
       <c r="E166" s="51" t="s">
-        <v>990</v>
+        <v>989</v>
       </c>
       <c r="F166" s="34" t="s">
         <v>252</v>
@@ -11221,7 +11218,7 @@
         <v>253</v>
       </c>
       <c r="E167" s="51" t="s">
-        <v>990</v>
+        <v>989</v>
       </c>
       <c r="F167" s="34" t="s">
         <v>254</v>
@@ -11263,7 +11260,7 @@
         <v>253</v>
       </c>
       <c r="E168" s="51" t="s">
-        <v>990</v>
+        <v>989</v>
       </c>
       <c r="F168" s="34" t="s">
         <v>254</v>
@@ -11305,7 +11302,7 @@
         <v>253</v>
       </c>
       <c r="E169" s="51" t="s">
-        <v>990</v>
+        <v>989</v>
       </c>
       <c r="F169" s="34" t="s">
         <v>254</v>
@@ -11347,7 +11344,7 @@
         <v>247</v>
       </c>
       <c r="E170" s="51" t="s">
-        <v>990</v>
+        <v>989</v>
       </c>
       <c r="F170" s="34" t="s">
         <v>249</v>
@@ -11389,7 +11386,7 @@
         <v>255</v>
       </c>
       <c r="E171" s="51" t="s">
-        <v>990</v>
+        <v>989</v>
       </c>
       <c r="F171" s="34" t="s">
         <v>171</v>
@@ -11431,7 +11428,7 @@
         <v>247</v>
       </c>
       <c r="E172" s="51" t="s">
-        <v>990</v>
+        <v>989</v>
       </c>
       <c r="F172" s="34" t="s">
         <v>246</v>
@@ -11473,7 +11470,7 @@
         <v>247</v>
       </c>
       <c r="E173" s="51" t="s">
-        <v>990</v>
+        <v>989</v>
       </c>
       <c r="F173" s="34" t="s">
         <v>246</v>
@@ -11515,7 +11512,7 @@
         <v>256</v>
       </c>
       <c r="E174" s="51" t="s">
-        <v>990</v>
+        <v>989</v>
       </c>
       <c r="F174" s="34" t="s">
         <v>257</v>
@@ -11557,7 +11554,7 @@
         <v>258</v>
       </c>
       <c r="E175" s="51" t="s">
-        <v>990</v>
+        <v>989</v>
       </c>
       <c r="F175" s="34" t="s">
         <v>171</v>
@@ -11599,7 +11596,7 @@
         <v>258</v>
       </c>
       <c r="E176" s="51" t="s">
-        <v>990</v>
+        <v>989</v>
       </c>
       <c r="F176" s="34" t="s">
         <v>171</v>
@@ -11641,7 +11638,7 @@
         <v>256</v>
       </c>
       <c r="E177" s="51" t="s">
-        <v>990</v>
+        <v>989</v>
       </c>
       <c r="F177" s="34" t="s">
         <v>257</v>
@@ -11683,7 +11680,7 @@
         <v>256</v>
       </c>
       <c r="E178" s="51" t="s">
-        <v>990</v>
+        <v>989</v>
       </c>
       <c r="F178" s="34" t="s">
         <v>259</v>
@@ -11725,7 +11722,7 @@
         <v>256</v>
       </c>
       <c r="E179" s="51" t="s">
-        <v>990</v>
+        <v>989</v>
       </c>
       <c r="F179" s="34" t="s">
         <v>259</v>
@@ -11767,7 +11764,7 @@
         <v>260</v>
       </c>
       <c r="E180" s="51" t="s">
-        <v>990</v>
+        <v>989</v>
       </c>
       <c r="F180" s="34" t="s">
         <v>261</v>
@@ -11811,7 +11808,7 @@
         <v>260</v>
       </c>
       <c r="E181" s="51" t="s">
-        <v>990</v>
+        <v>989</v>
       </c>
       <c r="F181" s="34" t="s">
         <v>262</v>
@@ -11853,7 +11850,7 @@
         <v>260</v>
       </c>
       <c r="E182" s="51" t="s">
-        <v>990</v>
+        <v>989</v>
       </c>
       <c r="F182" s="34" t="s">
         <v>262</v>
@@ -11895,7 +11892,7 @@
         <v>260</v>
       </c>
       <c r="E183" s="51" t="s">
-        <v>990</v>
+        <v>989</v>
       </c>
       <c r="F183" s="34" t="s">
         <v>263</v>
@@ -11937,7 +11934,7 @@
         <v>260</v>
       </c>
       <c r="E184" s="51" t="s">
-        <v>990</v>
+        <v>989</v>
       </c>
       <c r="F184" s="34" t="s">
         <v>263</v>
@@ -11979,7 +11976,7 @@
         <v>260</v>
       </c>
       <c r="E185" s="51" t="s">
-        <v>990</v>
+        <v>989</v>
       </c>
       <c r="F185" s="34" t="s">
         <v>264</v>
@@ -12021,7 +12018,7 @@
         <v>260</v>
       </c>
       <c r="E186" s="51" t="s">
-        <v>990</v>
+        <v>989</v>
       </c>
       <c r="F186" s="34" t="s">
         <v>264</v>
@@ -12063,7 +12060,7 @@
         <v>260</v>
       </c>
       <c r="E187" s="51" t="s">
-        <v>990</v>
+        <v>989</v>
       </c>
       <c r="F187" s="34" t="s">
         <v>265</v>
@@ -12105,7 +12102,7 @@
         <v>266</v>
       </c>
       <c r="E188" s="51" t="s">
-        <v>990</v>
+        <v>989</v>
       </c>
       <c r="F188" s="34" t="s">
         <v>267</v>
@@ -12147,7 +12144,7 @@
         <v>260</v>
       </c>
       <c r="E189" s="51" t="s">
-        <v>990</v>
+        <v>989</v>
       </c>
       <c r="F189" s="34" t="s">
         <v>268</v>
@@ -12189,7 +12186,7 @@
         <v>269</v>
       </c>
       <c r="E190" s="51" t="s">
-        <v>990</v>
+        <v>989</v>
       </c>
       <c r="F190" s="34" t="s">
         <v>270</v>
@@ -12231,7 +12228,7 @@
         <v>271</v>
       </c>
       <c r="E191" s="51" t="s">
-        <v>990</v>
+        <v>989</v>
       </c>
       <c r="F191" s="34" t="s">
         <v>272</v>
@@ -12273,7 +12270,7 @@
         <v>271</v>
       </c>
       <c r="E192" s="51" t="s">
-        <v>990</v>
+        <v>989</v>
       </c>
       <c r="F192" s="34" t="s">
         <v>272</v>
@@ -12315,7 +12312,7 @@
         <v>273</v>
       </c>
       <c r="E193" s="51" t="s">
-        <v>990</v>
+        <v>989</v>
       </c>
       <c r="F193" s="34" t="s">
         <v>274</v>
@@ -12357,7 +12354,7 @@
         <v>273</v>
       </c>
       <c r="E194" s="51" t="s">
-        <v>990</v>
+        <v>989</v>
       </c>
       <c r="F194" s="34" t="s">
         <v>275</v>
@@ -12399,7 +12396,7 @@
         <v>197</v>
       </c>
       <c r="E195" s="51" t="s">
-        <v>990</v>
+        <v>989</v>
       </c>
       <c r="F195" s="34" t="s">
         <v>276</v>
@@ -12443,7 +12440,7 @@
         <v>197</v>
       </c>
       <c r="E196" s="51" t="s">
-        <v>990</v>
+        <v>989</v>
       </c>
       <c r="F196" s="34" t="s">
         <v>277</v>
@@ -12485,7 +12482,7 @@
         <v>197</v>
       </c>
       <c r="E197" s="51" t="s">
-        <v>990</v>
+        <v>989</v>
       </c>
       <c r="F197" s="34" t="s">
         <v>278</v>
@@ -12529,7 +12526,7 @@
         <v>197</v>
       </c>
       <c r="E198" s="51" t="s">
-        <v>990</v>
+        <v>989</v>
       </c>
       <c r="F198" s="34" t="s">
         <v>278</v>
@@ -12571,7 +12568,7 @@
         <v>197</v>
       </c>
       <c r="E199" s="51" t="s">
-        <v>990</v>
+        <v>989</v>
       </c>
       <c r="F199" s="34" t="s">
         <v>279</v>
@@ -12613,7 +12610,7 @@
         <v>197</v>
       </c>
       <c r="E200" s="51" t="s">
-        <v>990</v>
+        <v>989</v>
       </c>
       <c r="F200" s="34" t="s">
         <v>279</v>
@@ -12657,7 +12654,7 @@
         <v>195</v>
       </c>
       <c r="E201" s="51" t="s">
-        <v>990</v>
+        <v>989</v>
       </c>
       <c r="F201" s="34" t="s">
         <v>280</v>
@@ -12699,7 +12696,7 @@
         <v>195</v>
       </c>
       <c r="E202" s="51" t="s">
-        <v>990</v>
+        <v>989</v>
       </c>
       <c r="F202" s="34" t="s">
         <v>281</v>
@@ -12743,7 +12740,7 @@
         <v>282</v>
       </c>
       <c r="E203" s="51" t="s">
-        <v>990</v>
+        <v>989</v>
       </c>
       <c r="F203" s="34" t="s">
         <v>283</v>
@@ -12785,7 +12782,7 @@
         <v>284</v>
       </c>
       <c r="E204" s="51" t="s">
-        <v>990</v>
+        <v>989</v>
       </c>
       <c r="F204" s="34" t="s">
         <v>285</v>
@@ -12829,7 +12826,7 @@
         <v>282</v>
       </c>
       <c r="E205" s="51" t="s">
-        <v>990</v>
+        <v>989</v>
       </c>
       <c r="F205" s="34" t="s">
         <v>286</v>
@@ -12873,7 +12870,7 @@
         <v>287</v>
       </c>
       <c r="E206" s="51" t="s">
-        <v>990</v>
+        <v>989</v>
       </c>
       <c r="F206" s="34" t="s">
         <v>283</v>
@@ -12915,7 +12912,7 @@
         <v>282</v>
       </c>
       <c r="E207" s="51" t="s">
-        <v>990</v>
+        <v>989</v>
       </c>
       <c r="F207" s="34" t="s">
         <v>288</v>
@@ -12957,7 +12954,7 @@
         <v>282</v>
       </c>
       <c r="E208" s="51" t="s">
-        <v>990</v>
+        <v>989</v>
       </c>
       <c r="F208" s="34" t="s">
         <v>289</v>
@@ -13001,7 +12998,7 @@
         <v>290</v>
       </c>
       <c r="E209" s="51" t="s">
-        <v>990</v>
+        <v>989</v>
       </c>
       <c r="F209" s="34" t="s">
         <v>291</v>
@@ -13045,7 +13042,7 @@
         <v>290</v>
       </c>
       <c r="E210" s="51" t="s">
-        <v>990</v>
+        <v>989</v>
       </c>
       <c r="F210" s="34" t="s">
         <v>292</v>
@@ -13089,7 +13086,7 @@
         <v>293</v>
       </c>
       <c r="E211" s="51" t="s">
-        <v>990</v>
+        <v>989</v>
       </c>
       <c r="F211" s="34" t="s">
         <v>294</v>
@@ -13131,7 +13128,7 @@
         <v>295</v>
       </c>
       <c r="E212" s="51" t="s">
-        <v>990</v>
+        <v>989</v>
       </c>
       <c r="F212" s="34" t="s">
         <v>296</v>
@@ -13173,7 +13170,7 @@
         <v>297</v>
       </c>
       <c r="E213" s="51" t="s">
-        <v>990</v>
+        <v>989</v>
       </c>
       <c r="F213" s="34" t="s">
         <v>298</v>
@@ -13217,7 +13214,7 @@
         <v>299</v>
       </c>
       <c r="E214" s="51" t="s">
-        <v>990</v>
+        <v>989</v>
       </c>
       <c r="F214" s="34" t="s">
         <v>300</v>
@@ -13259,7 +13256,7 @@
         <v>299</v>
       </c>
       <c r="E215" s="51" t="s">
-        <v>990</v>
+        <v>989</v>
       </c>
       <c r="F215" s="34" t="s">
         <v>300</v>
@@ -13301,7 +13298,7 @@
         <v>299</v>
       </c>
       <c r="E216" s="51" t="s">
-        <v>990</v>
+        <v>989</v>
       </c>
       <c r="F216" s="34" t="s">
         <v>301</v>
@@ -13343,7 +13340,7 @@
         <v>299</v>
       </c>
       <c r="E217" s="51" t="s">
-        <v>990</v>
+        <v>989</v>
       </c>
       <c r="F217" s="34" t="s">
         <v>302</v>
@@ -13385,7 +13382,7 @@
         <v>299</v>
       </c>
       <c r="E218" s="51" t="s">
-        <v>990</v>
+        <v>989</v>
       </c>
       <c r="F218" s="34" t="s">
         <v>303</v>
@@ -13427,7 +13424,7 @@
         <v>299</v>
       </c>
       <c r="E219" s="51" t="s">
-        <v>990</v>
+        <v>989</v>
       </c>
       <c r="F219" s="34" t="s">
         <v>304</v>
@@ -13469,7 +13466,7 @@
         <v>305</v>
       </c>
       <c r="E220" s="51" t="s">
-        <v>990</v>
+        <v>989</v>
       </c>
       <c r="F220" s="34" t="s">
         <v>306</v>
@@ -13513,7 +13510,7 @@
         <v>305</v>
       </c>
       <c r="E221" s="51" t="s">
-        <v>990</v>
+        <v>989</v>
       </c>
       <c r="F221" s="34" t="s">
         <v>306</v>
@@ -13555,7 +13552,7 @@
         <v>191</v>
       </c>
       <c r="E222" s="51" t="s">
-        <v>990</v>
+        <v>989</v>
       </c>
       <c r="F222" s="34" t="s">
         <v>307</v>
@@ -13597,7 +13594,7 @@
         <v>191</v>
       </c>
       <c r="E223" s="51" t="s">
-        <v>990</v>
+        <v>989</v>
       </c>
       <c r="F223" s="34" t="s">
         <v>307</v>
@@ -13639,7 +13636,7 @@
         <v>191</v>
       </c>
       <c r="E224" s="51" t="s">
-        <v>990</v>
+        <v>989</v>
       </c>
       <c r="F224" s="34" t="s">
         <v>308</v>
@@ -13683,7 +13680,7 @@
         <v>191</v>
       </c>
       <c r="E225" s="51" t="s">
-        <v>990</v>
+        <v>989</v>
       </c>
       <c r="F225" s="34" t="s">
         <v>309</v>
@@ -13725,7 +13722,7 @@
         <v>305</v>
       </c>
       <c r="E226" s="51" t="s">
-        <v>990</v>
+        <v>989</v>
       </c>
       <c r="F226" s="34" t="s">
         <v>310</v>
@@ -13767,7 +13764,7 @@
         <v>311</v>
       </c>
       <c r="E227" s="51" t="s">
-        <v>990</v>
+        <v>989</v>
       </c>
       <c r="F227" s="34" t="s">
         <v>312</v>
@@ -13809,7 +13806,7 @@
         <v>149</v>
       </c>
       <c r="E228" s="51" t="s">
-        <v>990</v>
+        <v>989</v>
       </c>
       <c r="F228" s="34" t="s">
         <v>313</v>
@@ -13853,7 +13850,7 @@
         <v>149</v>
       </c>
       <c r="E229" s="51" t="s">
-        <v>990</v>
+        <v>989</v>
       </c>
       <c r="F229" s="34" t="s">
         <v>313</v>
@@ -13897,7 +13894,7 @@
         <v>314</v>
       </c>
       <c r="E230" s="51" t="s">
-        <v>990</v>
+        <v>989</v>
       </c>
       <c r="F230" s="34" t="s">
         <v>315</v>
@@ -13941,7 +13938,7 @@
         <v>316</v>
       </c>
       <c r="E231" s="51" t="s">
-        <v>990</v>
+        <v>989</v>
       </c>
       <c r="F231" s="34" t="s">
         <v>317</v>
@@ -13983,7 +13980,7 @@
         <v>149</v>
       </c>
       <c r="E232" s="51" t="s">
-        <v>990</v>
+        <v>989</v>
       </c>
       <c r="F232" s="34" t="s">
         <v>318</v>
@@ -14025,7 +14022,7 @@
         <v>149</v>
       </c>
       <c r="E233" s="51" t="s">
-        <v>990</v>
+        <v>989</v>
       </c>
       <c r="F233" s="34" t="s">
         <v>319</v>
@@ -14069,7 +14066,7 @@
         <v>149</v>
       </c>
       <c r="E234" s="51" t="s">
-        <v>990</v>
+        <v>989</v>
       </c>
       <c r="F234" s="34" t="s">
         <v>319</v>
@@ -14111,7 +14108,7 @@
         <v>149</v>
       </c>
       <c r="E235" s="51" t="s">
-        <v>990</v>
+        <v>989</v>
       </c>
       <c r="F235" s="34" t="s">
         <v>319</v>
@@ -14153,7 +14150,7 @@
         <v>149</v>
       </c>
       <c r="E236" s="51" t="s">
-        <v>990</v>
+        <v>989</v>
       </c>
       <c r="F236" s="34" t="s">
         <v>319</v>
@@ -14195,7 +14192,7 @@
         <v>320</v>
       </c>
       <c r="E237" s="51" t="s">
-        <v>990</v>
+        <v>989</v>
       </c>
       <c r="F237" s="34" t="s">
         <v>321</v>
@@ -14239,7 +14236,7 @@
         <v>320</v>
       </c>
       <c r="E238" s="51" t="s">
-        <v>990</v>
+        <v>989</v>
       </c>
       <c r="F238" s="34" t="s">
         <v>321</v>
@@ -14281,7 +14278,7 @@
         <v>320</v>
       </c>
       <c r="E239" s="51" t="s">
-        <v>990</v>
+        <v>989</v>
       </c>
       <c r="F239" s="34" t="s">
         <v>322</v>
@@ -14323,7 +14320,7 @@
         <v>320</v>
       </c>
       <c r="E240" s="51" t="s">
-        <v>990</v>
+        <v>989</v>
       </c>
       <c r="F240" s="34" t="s">
         <v>323</v>
@@ -14365,7 +14362,7 @@
         <v>320</v>
       </c>
       <c r="E241" s="51" t="s">
-        <v>990</v>
+        <v>989</v>
       </c>
       <c r="F241" s="34" t="s">
         <v>324</v>
@@ -14407,7 +14404,7 @@
         <v>320</v>
       </c>
       <c r="E242" s="51" t="s">
-        <v>990</v>
+        <v>989</v>
       </c>
       <c r="F242" s="34" t="s">
         <v>324</v>
@@ -14449,7 +14446,7 @@
         <v>151</v>
       </c>
       <c r="E243" s="51" t="s">
-        <v>990</v>
+        <v>989</v>
       </c>
       <c r="F243" s="34" t="s">
         <v>325</v>
@@ -14493,7 +14490,7 @@
         <v>151</v>
       </c>
       <c r="E244" s="51" t="s">
-        <v>990</v>
+        <v>989</v>
       </c>
       <c r="F244" s="34" t="s">
         <v>326</v>
@@ -14535,7 +14532,7 @@
         <v>151</v>
       </c>
       <c r="E245" s="51" t="s">
-        <v>990</v>
+        <v>989</v>
       </c>
       <c r="F245" s="34" t="s">
         <v>326</v>
@@ -14577,7 +14574,7 @@
         <v>151</v>
       </c>
       <c r="E246" s="51" t="s">
-        <v>985</v>
+        <v>984</v>
       </c>
       <c r="F246" s="34" t="s">
         <v>327</v>
@@ -14661,7 +14658,7 @@
         <v>187</v>
       </c>
       <c r="E248" s="51" t="s">
-        <v>984</v>
+        <v>983</v>
       </c>
       <c r="F248" s="34" t="s">
         <v>329</v>
@@ -14705,7 +14702,7 @@
         <v>331</v>
       </c>
       <c r="E249" s="51" t="s">
-        <v>984</v>
+        <v>983</v>
       </c>
       <c r="F249" s="51" t="s">
         <v>336</v>
@@ -14747,7 +14744,7 @@
         <v>331</v>
       </c>
       <c r="E250" s="91" t="s">
-        <v>980</v>
+        <v>979</v>
       </c>
       <c r="F250" s="64" t="s">
         <v>13</v>
@@ -14787,7 +14784,7 @@
         <v>337</v>
       </c>
       <c r="E251" s="51" t="s">
-        <v>981</v>
+        <v>980</v>
       </c>
       <c r="F251" s="51" t="s">
         <v>338</v>
@@ -14871,7 +14868,7 @@
         <v>337</v>
       </c>
       <c r="E253" s="51" t="s">
-        <v>989</v>
+        <v>988</v>
       </c>
       <c r="F253" s="51" t="s">
         <v>342</v>
@@ -14911,7 +14908,7 @@
         <v>337</v>
       </c>
       <c r="E254" s="91" t="s">
-        <v>980</v>
+        <v>979</v>
       </c>
       <c r="F254" s="64" t="s">
         <v>13</v>
@@ -14949,7 +14946,7 @@
         <v>770</v>
       </c>
       <c r="E255" s="91" t="s">
-        <v>980</v>
+        <v>979</v>
       </c>
       <c r="F255" s="64" t="s">
         <v>13</v>
@@ -14987,7 +14984,7 @@
         <v>771</v>
       </c>
       <c r="E256" s="91" t="s">
-        <v>980</v>
+        <v>979</v>
       </c>
       <c r="F256" s="64" t="s">
         <v>13</v>
@@ -15025,7 +15022,7 @@
         <v>772</v>
       </c>
       <c r="E257" s="91" t="s">
-        <v>980</v>
+        <v>979</v>
       </c>
       <c r="F257" s="64" t="s">
         <v>13</v>
@@ -15063,7 +15060,7 @@
         <v>773</v>
       </c>
       <c r="E258" s="91" t="s">
-        <v>980</v>
+        <v>979</v>
       </c>
       <c r="F258" s="74" t="s">
         <v>13</v>
@@ -15101,7 +15098,7 @@
         <v>774</v>
       </c>
       <c r="E259" s="91" t="s">
-        <v>980</v>
+        <v>979</v>
       </c>
       <c r="F259" s="88" t="s">
         <v>13</v>
@@ -15141,7 +15138,7 @@
         <v>170</v>
       </c>
       <c r="E260" s="94" t="s">
-        <v>984</v>
+        <v>983</v>
       </c>
       <c r="F260" s="80" t="s">
         <v>343</v>
@@ -15183,7 +15180,7 @@
       </c>
       <c r="D261" s="55"/>
       <c r="E261" s="7" t="s">
-        <v>989</v>
+        <v>988</v>
       </c>
       <c r="F261" s="55" t="s">
         <v>344</v>
@@ -15224,7 +15221,7 @@
         <v>532</v>
       </c>
       <c r="D262" s="55" t="s">
-        <v>991</v>
+        <v>990</v>
       </c>
       <c r="E262" s="55" t="s">
         <v>78</v>
@@ -15257,7 +15254,7 @@
         <v>539</v>
       </c>
       <c r="Q262" s="62" t="s">
-        <v>996</v>
+        <v>993</v>
       </c>
     </row>
     <row r="263" spans="1:17" ht="35.25" x14ac:dyDescent="0.55000000000000004">
@@ -15313,10 +15310,10 @@
         <v>531</v>
       </c>
       <c r="D264" s="55" t="s">
-        <v>991</v>
+        <v>990</v>
       </c>
       <c r="E264" s="55" t="s">
-        <v>984</v>
+        <v>983</v>
       </c>
       <c r="F264" s="55" t="s">
         <v>346</v>
@@ -15346,7 +15343,7 @@
         <v>539</v>
       </c>
       <c r="Q264" s="62" t="s">
-        <v>996</v>
+        <v>993</v>
       </c>
     </row>
     <row r="265" spans="1:17" ht="23.5" x14ac:dyDescent="0.55000000000000004">
@@ -15360,10 +15357,10 @@
         <v>531</v>
       </c>
       <c r="D265" s="99" t="s">
-        <v>991</v>
+        <v>990</v>
       </c>
       <c r="E265" s="99" t="s">
-        <v>984</v>
+        <v>983</v>
       </c>
       <c r="F265" s="99" t="s">
         <v>347</v>
@@ -15393,7 +15390,7 @@
         <v>539</v>
       </c>
       <c r="Q265" s="62" t="s">
-        <v>996</v>
+        <v>993</v>
       </c>
     </row>
     <row r="266" spans="1:17" x14ac:dyDescent="0.55000000000000004">
@@ -15408,7 +15405,7 @@
         <v>547</v>
       </c>
       <c r="E266" s="91" t="s">
-        <v>980</v>
+        <v>979</v>
       </c>
       <c r="F266" s="89" t="s">
         <v>13</v>
@@ -15418,7 +15415,7 @@
       </c>
       <c r="H266" s="66"/>
       <c r="I266" s="86" t="s">
-        <v>993</v>
+        <v>994</v>
       </c>
       <c r="J266" s="86" t="s">
         <v>970</v>
@@ -15436,7 +15433,7 @@
         <v>33.24</v>
       </c>
       <c r="Q266" s="62" t="s">
-        <v>994</v>
+        <v>992</v>
       </c>
     </row>
     <row r="267" spans="1:17" x14ac:dyDescent="0.55000000000000004">
@@ -15451,7 +15448,7 @@
         <v>548</v>
       </c>
       <c r="E267" s="91" t="s">
-        <v>980</v>
+        <v>979</v>
       </c>
       <c r="F267" s="89" t="s">
         <v>13</v>
@@ -15489,7 +15486,7 @@
         <v>549</v>
       </c>
       <c r="E268" s="91" t="s">
-        <v>980</v>
+        <v>979</v>
       </c>
       <c r="F268" s="89" t="s">
         <v>13</v>
@@ -15499,7 +15496,7 @@
       </c>
       <c r="H268" s="66"/>
       <c r="I268" s="86" t="s">
-        <v>995</v>
+        <v>994</v>
       </c>
       <c r="J268" s="86" t="s">
         <v>970</v>
@@ -15517,7 +15514,7 @@
         <v>7.53</v>
       </c>
       <c r="Q268" s="62" t="s">
-        <v>994</v>
+        <v>992</v>
       </c>
     </row>
     <row r="269" spans="1:17" x14ac:dyDescent="0.55000000000000004">
@@ -15532,7 +15529,7 @@
         <v>550</v>
       </c>
       <c r="E269" s="91" t="s">
-        <v>980</v>
+        <v>979</v>
       </c>
       <c r="F269" s="89" t="s">
         <v>13</v>
@@ -15542,7 +15539,7 @@
       </c>
       <c r="H269" s="66"/>
       <c r="I269" s="86" t="s">
-        <v>995</v>
+        <v>994</v>
       </c>
       <c r="J269" s="86" t="s">
         <v>970</v>
@@ -15560,7 +15557,7 @@
         <v>7.7</v>
       </c>
       <c r="Q269" s="62" t="s">
-        <v>994</v>
+        <v>992</v>
       </c>
     </row>
     <row r="270" spans="1:17" x14ac:dyDescent="0.55000000000000004">
@@ -15575,7 +15572,7 @@
         <v>727</v>
       </c>
       <c r="E270" s="91" t="s">
-        <v>980</v>
+        <v>979</v>
       </c>
       <c r="F270" s="89" t="s">
         <v>13</v>
@@ -15613,7 +15610,7 @@
         <v>554</v>
       </c>
       <c r="E271" s="91" t="s">
-        <v>980</v>
+        <v>979</v>
       </c>
       <c r="F271" s="89" t="s">
         <v>13</v>
@@ -15651,7 +15648,7 @@
         <v>271</v>
       </c>
       <c r="E272" s="91" t="s">
-        <v>980</v>
+        <v>979</v>
       </c>
       <c r="F272" s="89" t="s">
         <v>13</v>
@@ -15661,7 +15658,7 @@
       </c>
       <c r="H272" s="66"/>
       <c r="I272" s="86" t="s">
-        <v>995</v>
+        <v>994</v>
       </c>
       <c r="J272" s="86" t="s">
         <v>970</v>
@@ -15679,7 +15676,7 @@
         <v>41.8</v>
       </c>
       <c r="Q272" s="62" t="s">
-        <v>994</v>
+        <v>992</v>
       </c>
     </row>
     <row r="273" spans="1:17" x14ac:dyDescent="0.55000000000000004">
@@ -15694,7 +15691,7 @@
         <v>551</v>
       </c>
       <c r="E273" s="91" t="s">
-        <v>980</v>
+        <v>979</v>
       </c>
       <c r="F273" s="89" t="s">
         <v>13</v>
@@ -15704,7 +15701,7 @@
       </c>
       <c r="H273" s="66"/>
       <c r="I273" s="86" t="s">
-        <v>995</v>
+        <v>994</v>
       </c>
       <c r="J273" s="86" t="s">
         <v>970</v>
@@ -15722,7 +15719,7 @@
         <v>32.54</v>
       </c>
       <c r="Q273" s="62" t="s">
-        <v>994</v>
+        <v>992</v>
       </c>
     </row>
     <row r="274" spans="1:17" x14ac:dyDescent="0.55000000000000004">
@@ -15737,7 +15734,7 @@
         <v>552</v>
       </c>
       <c r="E274" s="91" t="s">
-        <v>980</v>
+        <v>979</v>
       </c>
       <c r="F274" s="89" t="s">
         <v>13</v>
@@ -15747,7 +15744,7 @@
       </c>
       <c r="H274" s="66"/>
       <c r="I274" s="86" t="s">
-        <v>995</v>
+        <v>994</v>
       </c>
       <c r="J274" s="86" t="s">
         <v>970</v>
@@ -15765,7 +15762,7 @@
         <v>37.04</v>
       </c>
       <c r="Q274" s="62" t="s">
-        <v>994</v>
+        <v>992</v>
       </c>
     </row>
     <row r="275" spans="1:17" x14ac:dyDescent="0.55000000000000004">
@@ -15780,7 +15777,7 @@
         <v>553</v>
       </c>
       <c r="E275" s="91" t="s">
-        <v>980</v>
+        <v>979</v>
       </c>
       <c r="F275" s="89" t="s">
         <v>13</v>
@@ -15790,7 +15787,7 @@
       </c>
       <c r="H275" s="66"/>
       <c r="I275" s="86" t="s">
-        <v>995</v>
+        <v>994</v>
       </c>
       <c r="J275" s="86" t="s">
         <v>970</v>
@@ -15808,7 +15805,7 @@
         <v>120.85</v>
       </c>
       <c r="Q275" s="62" t="s">
-        <v>994</v>
+        <v>992</v>
       </c>
     </row>
     <row r="276" spans="1:17" x14ac:dyDescent="0.55000000000000004">
@@ -15823,7 +15820,7 @@
         <v>189</v>
       </c>
       <c r="E276" s="91" t="s">
-        <v>980</v>
+        <v>979</v>
       </c>
       <c r="F276" s="89" t="s">
         <v>13</v>
@@ -15833,7 +15830,7 @@
       </c>
       <c r="H276" s="66"/>
       <c r="I276" s="86" t="s">
-        <v>995</v>
+        <v>994</v>
       </c>
       <c r="J276" s="86" t="s">
         <v>970</v>
@@ -15851,7 +15848,7 @@
         <v>13.53</v>
       </c>
       <c r="Q276" s="62" t="s">
-        <v>994</v>
+        <v>992</v>
       </c>
     </row>
     <row r="277" spans="1:17" x14ac:dyDescent="0.55000000000000004">
@@ -15866,7 +15863,7 @@
         <v>557</v>
       </c>
       <c r="E277" s="91" t="s">
-        <v>980</v>
+        <v>979</v>
       </c>
       <c r="F277" s="89" t="s">
         <v>13</v>
@@ -15876,7 +15873,7 @@
       </c>
       <c r="H277" s="66"/>
       <c r="I277" s="86" t="s">
-        <v>995</v>
+        <v>994</v>
       </c>
       <c r="J277" s="86" t="s">
         <v>970</v>
@@ -15894,7 +15891,7 @@
         <v>13.71</v>
       </c>
       <c r="Q277" s="62" t="s">
-        <v>994</v>
+        <v>992</v>
       </c>
     </row>
     <row r="278" spans="1:17" x14ac:dyDescent="0.55000000000000004">
@@ -15909,7 +15906,7 @@
         <v>555</v>
       </c>
       <c r="E278" s="91" t="s">
-        <v>980</v>
+        <v>979</v>
       </c>
       <c r="F278" s="89" t="s">
         <v>13</v>
@@ -15919,7 +15916,7 @@
       </c>
       <c r="H278" s="66"/>
       <c r="I278" s="86" t="s">
-        <v>995</v>
+        <v>994</v>
       </c>
       <c r="J278" s="86" t="s">
         <v>970</v>
@@ -15937,7 +15934,7 @@
         <v>11.7</v>
       </c>
       <c r="Q278" s="62" t="s">
-        <v>994</v>
+        <v>992</v>
       </c>
     </row>
     <row r="279" spans="1:17" x14ac:dyDescent="0.55000000000000004">
@@ -15952,7 +15949,7 @@
         <v>556</v>
       </c>
       <c r="E279" s="91" t="s">
-        <v>980</v>
+        <v>979</v>
       </c>
       <c r="F279" s="89" t="s">
         <v>13</v>
@@ -15962,7 +15959,7 @@
       </c>
       <c r="H279" s="66"/>
       <c r="I279" s="86" t="s">
-        <v>995</v>
+        <v>994</v>
       </c>
       <c r="J279" s="86" t="s">
         <v>970</v>
@@ -15980,7 +15977,7 @@
         <v>19.32</v>
       </c>
       <c r="Q279" s="62" t="s">
-        <v>994</v>
+        <v>992</v>
       </c>
     </row>
     <row r="280" spans="1:17" x14ac:dyDescent="0.55000000000000004">
@@ -15995,7 +15992,7 @@
         <v>558</v>
       </c>
       <c r="E280" s="91" t="s">
-        <v>980</v>
+        <v>979</v>
       </c>
       <c r="F280" s="89" t="s">
         <v>13</v>
@@ -16005,7 +16002,7 @@
       </c>
       <c r="H280" s="66"/>
       <c r="I280" s="86" t="s">
-        <v>995</v>
+        <v>994</v>
       </c>
       <c r="J280" s="86" t="s">
         <v>970</v>
@@ -16023,7 +16020,7 @@
         <v>27.65</v>
       </c>
       <c r="Q280" s="62" t="s">
-        <v>994</v>
+        <v>992</v>
       </c>
     </row>
     <row r="281" spans="1:17" x14ac:dyDescent="0.55000000000000004">
@@ -16038,7 +16035,7 @@
         <v>559</v>
       </c>
       <c r="E281" s="91" t="s">
-        <v>980</v>
+        <v>979</v>
       </c>
       <c r="F281" s="89" t="s">
         <v>13</v>
@@ -16048,7 +16045,7 @@
       </c>
       <c r="H281" s="66"/>
       <c r="I281" s="86" t="s">
-        <v>995</v>
+        <v>994</v>
       </c>
       <c r="J281" s="86" t="s">
         <v>970</v>
@@ -16066,7 +16063,7 @@
         <v>77.319999999999993</v>
       </c>
       <c r="Q281" s="62" t="s">
-        <v>994</v>
+        <v>992</v>
       </c>
     </row>
     <row r="282" spans="1:17" x14ac:dyDescent="0.55000000000000004">
@@ -16081,7 +16078,7 @@
         <v>732</v>
       </c>
       <c r="E282" s="91" t="s">
-        <v>980</v>
+        <v>979</v>
       </c>
       <c r="F282" s="89" t="s">
         <v>13</v>
@@ -16091,7 +16088,7 @@
       </c>
       <c r="H282" s="66"/>
       <c r="I282" s="86" t="s">
-        <v>993</v>
+        <v>994</v>
       </c>
       <c r="J282" s="86" t="s">
         <v>970</v>
@@ -16109,7 +16106,7 @@
         <v>5.36</v>
       </c>
       <c r="Q282" s="62" t="s">
-        <v>994</v>
+        <v>992</v>
       </c>
     </row>
     <row r="283" spans="1:17" x14ac:dyDescent="0.55000000000000004">
@@ -16124,7 +16121,7 @@
         <v>565</v>
       </c>
       <c r="E283" s="91" t="s">
-        <v>980</v>
+        <v>979</v>
       </c>
       <c r="F283" s="89" t="s">
         <v>13</v>
@@ -16134,7 +16131,7 @@
       </c>
       <c r="H283" s="66"/>
       <c r="I283" s="86" t="s">
-        <v>993</v>
+        <v>994</v>
       </c>
       <c r="J283" s="86" t="s">
         <v>970</v>
@@ -16152,7 +16149,7 @@
         <v>10.59</v>
       </c>
       <c r="Q283" s="62" t="s">
-        <v>994</v>
+        <v>992</v>
       </c>
     </row>
     <row r="284" spans="1:17" x14ac:dyDescent="0.55000000000000004">
@@ -16167,7 +16164,7 @@
         <v>197</v>
       </c>
       <c r="E284" s="91" t="s">
-        <v>980</v>
+        <v>979</v>
       </c>
       <c r="F284" s="89" t="s">
         <v>13</v>
@@ -16177,7 +16174,7 @@
       </c>
       <c r="H284" s="66"/>
       <c r="I284" s="86" t="s">
-        <v>995</v>
+        <v>994</v>
       </c>
       <c r="J284" s="86" t="s">
         <v>970</v>
@@ -16195,7 +16192,7 @@
         <v>147.94</v>
       </c>
       <c r="Q284" s="62" t="s">
-        <v>994</v>
+        <v>992</v>
       </c>
     </row>
     <row r="285" spans="1:17" x14ac:dyDescent="0.55000000000000004">
@@ -16210,7 +16207,7 @@
         <v>560</v>
       </c>
       <c r="E285" s="91" t="s">
-        <v>980</v>
+        <v>979</v>
       </c>
       <c r="F285" s="89" t="s">
         <v>13</v>
@@ -16220,7 +16217,7 @@
       </c>
       <c r="H285" s="66"/>
       <c r="I285" s="86" t="s">
-        <v>993</v>
+        <v>994</v>
       </c>
       <c r="J285" s="86" t="s">
         <v>970</v>
@@ -16238,7 +16235,7 @@
         <v>30.07</v>
       </c>
       <c r="Q285" s="62" t="s">
-        <v>994</v>
+        <v>992</v>
       </c>
     </row>
     <row r="286" spans="1:17" x14ac:dyDescent="0.55000000000000004">
@@ -16253,7 +16250,7 @@
         <v>561</v>
       </c>
       <c r="E286" s="91" t="s">
-        <v>980</v>
+        <v>979</v>
       </c>
       <c r="F286" s="89" t="s">
         <v>13</v>
@@ -16263,7 +16260,7 @@
       </c>
       <c r="H286" s="66"/>
       <c r="I286" s="86" t="s">
-        <v>995</v>
+        <v>994</v>
       </c>
       <c r="J286" s="86" t="s">
         <v>970</v>
@@ -16281,7 +16278,7 @@
         <v>8.0500000000000007</v>
       </c>
       <c r="Q286" s="62" t="s">
-        <v>994</v>
+        <v>992</v>
       </c>
     </row>
     <row r="287" spans="1:17" x14ac:dyDescent="0.55000000000000004">
@@ -16296,7 +16293,7 @@
         <v>564</v>
       </c>
       <c r="E287" s="91" t="s">
-        <v>980</v>
+        <v>979</v>
       </c>
       <c r="F287" s="89" t="s">
         <v>13</v>
@@ -16306,7 +16303,7 @@
       </c>
       <c r="H287" s="66"/>
       <c r="I287" s="86" t="s">
-        <v>995</v>
+        <v>994</v>
       </c>
       <c r="J287" s="86" t="s">
         <v>970</v>
@@ -16324,7 +16321,7 @@
         <v>8.0299999999999994</v>
       </c>
       <c r="Q287" s="62" t="s">
-        <v>994</v>
+        <v>992</v>
       </c>
     </row>
     <row r="288" spans="1:17" x14ac:dyDescent="0.55000000000000004">
@@ -16339,7 +16336,7 @@
         <v>563</v>
       </c>
       <c r="E288" s="91" t="s">
-        <v>980</v>
+        <v>979</v>
       </c>
       <c r="F288" s="89" t="s">
         <v>13</v>
@@ -16375,7 +16372,7 @@
         <v>546</v>
       </c>
       <c r="E289" s="91" t="s">
-        <v>980</v>
+        <v>979</v>
       </c>
       <c r="F289" s="89" t="s">
         <v>13</v>
@@ -16385,7 +16382,7 @@
       </c>
       <c r="H289" s="66"/>
       <c r="I289" s="86" t="s">
-        <v>993</v>
+        <v>994</v>
       </c>
       <c r="J289" s="86" t="s">
         <v>970</v>
@@ -16403,7 +16400,7 @@
         <v>28.78</v>
       </c>
       <c r="Q289" s="62" t="s">
-        <v>994</v>
+        <v>992</v>
       </c>
     </row>
     <row r="290" spans="1:17" x14ac:dyDescent="0.55000000000000004">
@@ -16418,7 +16415,7 @@
         <v>733</v>
       </c>
       <c r="E290" s="91" t="s">
-        <v>980</v>
+        <v>979</v>
       </c>
       <c r="F290" s="89" t="s">
         <v>13</v>
@@ -16428,7 +16425,7 @@
       </c>
       <c r="H290" s="66"/>
       <c r="I290" s="86" t="s">
-        <v>995</v>
+        <v>994</v>
       </c>
       <c r="J290" s="86" t="s">
         <v>970</v>
@@ -16446,7 +16443,7 @@
         <v>9.51</v>
       </c>
       <c r="Q290" s="62" t="s">
-        <v>994</v>
+        <v>992</v>
       </c>
     </row>
     <row r="291" spans="1:17" x14ac:dyDescent="0.55000000000000004">
@@ -16461,7 +16458,7 @@
         <v>734</v>
       </c>
       <c r="E291" s="91" t="s">
-        <v>980</v>
+        <v>979</v>
       </c>
       <c r="F291" s="89" t="s">
         <v>13</v>
@@ -16471,7 +16468,7 @@
       </c>
       <c r="H291" s="66"/>
       <c r="I291" s="86" t="s">
-        <v>995</v>
+        <v>994</v>
       </c>
       <c r="J291" s="86" t="s">
         <v>970</v>
@@ -16489,7 +16486,7 @@
         <v>16.2</v>
       </c>
       <c r="Q291" s="62" t="s">
-        <v>994</v>
+        <v>992</v>
       </c>
     </row>
     <row r="292" spans="1:17" x14ac:dyDescent="0.55000000000000004">
@@ -16504,7 +16501,7 @@
         <v>866</v>
       </c>
       <c r="E292" s="91" t="s">
-        <v>980</v>
+        <v>979</v>
       </c>
       <c r="F292" s="89" t="s">
         <v>13</v>
@@ -16514,7 +16511,7 @@
       </c>
       <c r="H292" s="66"/>
       <c r="I292" s="86" t="s">
-        <v>995</v>
+        <v>994</v>
       </c>
       <c r="J292" s="86" t="s">
         <v>970</v>
@@ -16532,7 +16529,7 @@
         <v>2.6</v>
       </c>
       <c r="Q292" s="62" t="s">
-        <v>994</v>
+        <v>992</v>
       </c>
     </row>
     <row r="293" spans="1:17" x14ac:dyDescent="0.55000000000000004">
@@ -16547,7 +16544,7 @@
         <v>562</v>
       </c>
       <c r="E293" s="91" t="s">
-        <v>980</v>
+        <v>979</v>
       </c>
       <c r="F293" s="89" t="s">
         <v>13</v>
@@ -16557,7 +16554,7 @@
       </c>
       <c r="H293" s="66"/>
       <c r="I293" s="86" t="s">
-        <v>993</v>
+        <v>994</v>
       </c>
       <c r="J293" s="86" t="s">
         <v>970</v>
@@ -16575,7 +16572,7 @@
         <v>27.79</v>
       </c>
       <c r="Q293" s="62" t="s">
-        <v>994</v>
+        <v>992</v>
       </c>
     </row>
     <row r="294" spans="1:17" x14ac:dyDescent="0.55000000000000004">
@@ -16590,7 +16587,7 @@
         <v>566</v>
       </c>
       <c r="E294" s="91" t="s">
-        <v>980</v>
+        <v>979</v>
       </c>
       <c r="F294" s="89" t="s">
         <v>13</v>
@@ -16626,7 +16623,7 @@
         <v>567</v>
       </c>
       <c r="E295" s="91" t="s">
-        <v>980</v>
+        <v>979</v>
       </c>
       <c r="F295" s="89" t="s">
         <v>13</v>
@@ -16662,7 +16659,7 @@
         <v>568</v>
       </c>
       <c r="E296" s="91" t="s">
-        <v>980</v>
+        <v>979</v>
       </c>
       <c r="F296" s="89" t="s">
         <v>13</v>
@@ -16698,7 +16695,7 @@
         <v>569</v>
       </c>
       <c r="E297" s="91" t="s">
-        <v>980</v>
+        <v>979</v>
       </c>
       <c r="F297" s="89" t="s">
         <v>13</v>
@@ -16734,7 +16731,7 @@
         <v>570</v>
       </c>
       <c r="E298" s="91" t="s">
-        <v>980</v>
+        <v>979</v>
       </c>
       <c r="F298" s="89" t="s">
         <v>13</v>
@@ -16770,7 +16767,7 @@
         <v>571</v>
       </c>
       <c r="E299" s="91" t="s">
-        <v>980</v>
+        <v>979</v>
       </c>
       <c r="F299" s="89" t="s">
         <v>13</v>
@@ -16806,7 +16803,7 @@
         <v>572</v>
       </c>
       <c r="E300" s="91" t="s">
-        <v>980</v>
+        <v>979</v>
       </c>
       <c r="F300" s="89" t="s">
         <v>13</v>
@@ -16842,7 +16839,7 @@
         <v>573</v>
       </c>
       <c r="E301" s="91" t="s">
-        <v>980</v>
+        <v>979</v>
       </c>
       <c r="F301" s="89" t="s">
         <v>13</v>
@@ -16878,7 +16875,7 @@
         <v>574</v>
       </c>
       <c r="E302" s="91" t="s">
-        <v>980</v>
+        <v>979</v>
       </c>
       <c r="F302" s="89" t="s">
         <v>13</v>
@@ -16914,7 +16911,7 @@
         <v>575</v>
       </c>
       <c r="E303" s="91" t="s">
-        <v>980</v>
+        <v>979</v>
       </c>
       <c r="F303" s="89" t="s">
         <v>13</v>
@@ -16950,7 +16947,7 @@
         <v>576</v>
       </c>
       <c r="E304" s="91" t="s">
-        <v>980</v>
+        <v>979</v>
       </c>
       <c r="F304" s="89" t="s">
         <v>13</v>
@@ -16986,7 +16983,7 @@
         <v>577</v>
       </c>
       <c r="E305" s="91" t="s">
-        <v>980</v>
+        <v>979</v>
       </c>
       <c r="F305" s="89" t="s">
         <v>13</v>
@@ -17022,7 +17019,7 @@
         <v>578</v>
       </c>
       <c r="E306" s="91" t="s">
-        <v>980</v>
+        <v>979</v>
       </c>
       <c r="F306" s="89" t="s">
         <v>13</v>
@@ -17058,7 +17055,7 @@
         <v>579</v>
       </c>
       <c r="E307" s="91" t="s">
-        <v>980</v>
+        <v>979</v>
       </c>
       <c r="F307" s="89" t="s">
         <v>13</v>
@@ -17094,7 +17091,7 @@
         <v>580</v>
       </c>
       <c r="E308" s="91" t="s">
-        <v>980</v>
+        <v>979</v>
       </c>
       <c r="F308" s="89" t="s">
         <v>13</v>
@@ -17130,7 +17127,7 @@
         <v>172</v>
       </c>
       <c r="E309" s="91" t="s">
-        <v>980</v>
+        <v>979</v>
       </c>
       <c r="F309" s="89" t="s">
         <v>13</v>
@@ -17166,7 +17163,7 @@
         <v>581</v>
       </c>
       <c r="E310" s="91" t="s">
-        <v>980</v>
+        <v>979</v>
       </c>
       <c r="F310" s="89" t="s">
         <v>13</v>
@@ -17202,7 +17199,7 @@
         <v>582</v>
       </c>
       <c r="E311" s="91" t="s">
-        <v>980</v>
+        <v>979</v>
       </c>
       <c r="F311" s="89" t="s">
         <v>13</v>
@@ -17238,7 +17235,7 @@
         <v>583</v>
       </c>
       <c r="E312" s="91" t="s">
-        <v>980</v>
+        <v>979</v>
       </c>
       <c r="F312" s="89" t="s">
         <v>13</v>
@@ -17274,7 +17271,7 @@
         <v>584</v>
       </c>
       <c r="E313" s="91" t="s">
-        <v>980</v>
+        <v>979</v>
       </c>
       <c r="F313" s="89" t="s">
         <v>13</v>
@@ -17310,7 +17307,7 @@
         <v>585</v>
       </c>
       <c r="E314" s="91" t="s">
-        <v>980</v>
+        <v>979</v>
       </c>
       <c r="F314" s="89" t="s">
         <v>13</v>
@@ -17346,7 +17343,7 @@
         <v>586</v>
       </c>
       <c r="E315" s="91" t="s">
-        <v>980</v>
+        <v>979</v>
       </c>
       <c r="F315" s="89" t="s">
         <v>13</v>
@@ -17382,7 +17379,7 @@
         <v>587</v>
       </c>
       <c r="E316" s="91" t="s">
-        <v>980</v>
+        <v>979</v>
       </c>
       <c r="F316" s="89" t="s">
         <v>13</v>
@@ -17418,7 +17415,7 @@
         <v>588</v>
       </c>
       <c r="E317" s="91" t="s">
-        <v>980</v>
+        <v>979</v>
       </c>
       <c r="F317" s="89" t="s">
         <v>13</v>
@@ -17454,7 +17451,7 @@
         <v>589</v>
       </c>
       <c r="E318" s="91" t="s">
-        <v>980</v>
+        <v>979</v>
       </c>
       <c r="F318" s="89" t="s">
         <v>13</v>
@@ -17490,7 +17487,7 @@
         <v>177</v>
       </c>
       <c r="E319" s="91" t="s">
-        <v>980</v>
+        <v>979</v>
       </c>
       <c r="F319" s="89" t="s">
         <v>13</v>
@@ -17526,7 +17523,7 @@
         <v>590</v>
       </c>
       <c r="E320" s="91" t="s">
-        <v>980</v>
+        <v>979</v>
       </c>
       <c r="F320" s="89" t="s">
         <v>13</v>
@@ -17562,7 +17559,7 @@
         <v>591</v>
       </c>
       <c r="E321" s="91" t="s">
-        <v>980</v>
+        <v>979</v>
       </c>
       <c r="F321" s="89" t="s">
         <v>13</v>
@@ -17598,7 +17595,7 @@
         <v>592</v>
       </c>
       <c r="E322" s="91" t="s">
-        <v>980</v>
+        <v>979</v>
       </c>
       <c r="F322" s="89" t="s">
         <v>13</v>
@@ -17634,7 +17631,7 @@
         <v>593</v>
       </c>
       <c r="E323" s="91" t="s">
-        <v>980</v>
+        <v>979</v>
       </c>
       <c r="F323" s="89" t="s">
         <v>13</v>
@@ -17670,7 +17667,7 @@
         <v>594</v>
       </c>
       <c r="E324" s="91" t="s">
-        <v>980</v>
+        <v>979</v>
       </c>
       <c r="F324" s="89" t="s">
         <v>13</v>
@@ -17706,7 +17703,7 @@
         <v>595</v>
       </c>
       <c r="E325" s="91" t="s">
-        <v>980</v>
+        <v>979</v>
       </c>
       <c r="F325" s="89" t="s">
         <v>13</v>
@@ -17742,7 +17739,7 @@
         <v>189</v>
       </c>
       <c r="E326" s="91" t="s">
-        <v>980</v>
+        <v>979</v>
       </c>
       <c r="F326" s="89" t="s">
         <v>13</v>
@@ -17752,7 +17749,7 @@
       </c>
       <c r="H326" s="66"/>
       <c r="I326" s="86" t="s">
-        <v>995</v>
+        <v>994</v>
       </c>
       <c r="J326" s="86" t="s">
         <v>970</v>
@@ -17770,7 +17767,7 @@
         <v>13.53</v>
       </c>
       <c r="Q326" s="62" t="s">
-        <v>994</v>
+        <v>992</v>
       </c>
     </row>
     <row r="327" spans="1:17" x14ac:dyDescent="0.55000000000000004">
@@ -17785,7 +17782,7 @@
         <v>590</v>
       </c>
       <c r="E327" s="91" t="s">
-        <v>980</v>
+        <v>979</v>
       </c>
       <c r="F327" s="89" t="s">
         <v>13</v>
@@ -17821,7 +17818,7 @@
         <v>596</v>
       </c>
       <c r="E328" s="91" t="s">
-        <v>980</v>
+        <v>979</v>
       </c>
       <c r="F328" s="89" t="s">
         <v>13</v>
@@ -17857,7 +17854,7 @@
         <v>597</v>
       </c>
       <c r="E329" s="91" t="s">
-        <v>980</v>
+        <v>979</v>
       </c>
       <c r="F329" s="89" t="s">
         <v>13</v>
@@ -17893,7 +17890,7 @@
         <v>591</v>
       </c>
       <c r="E330" s="91" t="s">
-        <v>980</v>
+        <v>979</v>
       </c>
       <c r="F330" s="89" t="s">
         <v>13</v>
@@ -17929,7 +17926,7 @@
         <v>592</v>
       </c>
       <c r="E331" s="91" t="s">
-        <v>980</v>
+        <v>979</v>
       </c>
       <c r="F331" s="89" t="s">
         <v>13</v>
@@ -17965,7 +17962,7 @@
         <v>598</v>
       </c>
       <c r="E332" s="91" t="s">
-        <v>980</v>
+        <v>979</v>
       </c>
       <c r="F332" s="89" t="s">
         <v>13</v>
@@ -18001,7 +17998,7 @@
         <v>599</v>
       </c>
       <c r="E333" s="91" t="s">
-        <v>980</v>
+        <v>979</v>
       </c>
       <c r="F333" s="89" t="s">
         <v>13</v>
@@ -18037,7 +18034,7 @@
         <v>600</v>
       </c>
       <c r="E334" s="91" t="s">
-        <v>980</v>
+        <v>979</v>
       </c>
       <c r="F334" s="89" t="s">
         <v>13</v>
@@ -18073,7 +18070,7 @@
         <v>601</v>
       </c>
       <c r="E335" s="91" t="s">
-        <v>980</v>
+        <v>979</v>
       </c>
       <c r="F335" s="89" t="s">
         <v>13</v>
@@ -18109,7 +18106,7 @@
         <v>602</v>
       </c>
       <c r="E336" s="91" t="s">
-        <v>980</v>
+        <v>979</v>
       </c>
       <c r="F336" s="89" t="s">
         <v>13</v>
@@ -18145,7 +18142,7 @@
         <v>603</v>
       </c>
       <c r="E337" s="91" t="s">
-        <v>980</v>
+        <v>979</v>
       </c>
       <c r="F337" s="89" t="s">
         <v>13</v>
@@ -18181,7 +18178,7 @@
         <v>604</v>
       </c>
       <c r="E338" s="91" t="s">
-        <v>980</v>
+        <v>979</v>
       </c>
       <c r="F338" s="89" t="s">
         <v>13</v>
@@ -18217,7 +18214,7 @@
         <v>605</v>
       </c>
       <c r="E339" s="91" t="s">
-        <v>980</v>
+        <v>979</v>
       </c>
       <c r="F339" s="89" t="s">
         <v>13</v>
@@ -18253,7 +18250,7 @@
         <v>606</v>
       </c>
       <c r="E340" s="91" t="s">
-        <v>980</v>
+        <v>979</v>
       </c>
       <c r="F340" s="89" t="s">
         <v>13</v>
@@ -18289,7 +18286,7 @@
         <v>607</v>
       </c>
       <c r="E341" s="91" t="s">
-        <v>980</v>
+        <v>979</v>
       </c>
       <c r="F341" s="89" t="s">
         <v>13</v>
@@ -18325,7 +18322,7 @@
         <v>608</v>
       </c>
       <c r="E342" s="91" t="s">
-        <v>980</v>
+        <v>979</v>
       </c>
       <c r="F342" s="89" t="s">
         <v>13</v>
@@ -18361,7 +18358,7 @@
         <v>609</v>
       </c>
       <c r="E343" s="91" t="s">
-        <v>980</v>
+        <v>979</v>
       </c>
       <c r="F343" s="89" t="s">
         <v>13</v>
@@ -18397,7 +18394,7 @@
         <v>610</v>
       </c>
       <c r="E344" s="91" t="s">
-        <v>980</v>
+        <v>979</v>
       </c>
       <c r="F344" s="89" t="s">
         <v>13</v>
@@ -18433,7 +18430,7 @@
         <v>167</v>
       </c>
       <c r="E345" s="91" t="s">
-        <v>980</v>
+        <v>979</v>
       </c>
       <c r="F345" s="89" t="s">
         <v>13</v>
@@ -18469,7 +18466,7 @@
         <v>611</v>
       </c>
       <c r="E346" s="91" t="s">
-        <v>980</v>
+        <v>979</v>
       </c>
       <c r="F346" s="89" t="s">
         <v>13</v>
@@ -18505,7 +18502,7 @@
         <v>229</v>
       </c>
       <c r="E347" s="91" t="s">
-        <v>980</v>
+        <v>979</v>
       </c>
       <c r="F347" s="89" t="s">
         <v>13</v>
@@ -18541,7 +18538,7 @@
         <v>612</v>
       </c>
       <c r="E348" s="91" t="s">
-        <v>980</v>
+        <v>979</v>
       </c>
       <c r="F348" s="89" t="s">
         <v>13</v>
@@ -18577,7 +18574,7 @@
         <v>613</v>
       </c>
       <c r="E349" s="91" t="s">
-        <v>980</v>
+        <v>979</v>
       </c>
       <c r="F349" s="89" t="s">
         <v>13</v>
@@ -18613,7 +18610,7 @@
         <v>235</v>
       </c>
       <c r="E350" s="91" t="s">
-        <v>980</v>
+        <v>979</v>
       </c>
       <c r="F350" s="89" t="s">
         <v>13</v>
@@ -18649,7 +18646,7 @@
         <v>614</v>
       </c>
       <c r="E351" s="91" t="s">
-        <v>980</v>
+        <v>979</v>
       </c>
       <c r="F351" s="89" t="s">
         <v>13</v>
@@ -18685,7 +18682,7 @@
         <v>615</v>
       </c>
       <c r="E352" s="91" t="s">
-        <v>980</v>
+        <v>979</v>
       </c>
       <c r="F352" s="89" t="s">
         <v>13</v>
@@ -18721,7 +18718,7 @@
         <v>231</v>
       </c>
       <c r="E353" s="91" t="s">
-        <v>980</v>
+        <v>979</v>
       </c>
       <c r="F353" s="89" t="s">
         <v>13</v>
@@ -18757,7 +18754,7 @@
         <v>238</v>
       </c>
       <c r="E354" s="91" t="s">
-        <v>980</v>
+        <v>979</v>
       </c>
       <c r="F354" s="89" t="s">
         <v>13</v>
@@ -18793,7 +18790,7 @@
         <v>233</v>
       </c>
       <c r="E355" s="91" t="s">
-        <v>980</v>
+        <v>979</v>
       </c>
       <c r="F355" s="89" t="s">
         <v>13</v>
@@ -18829,7 +18826,7 @@
         <v>616</v>
       </c>
       <c r="E356" s="91" t="s">
-        <v>980</v>
+        <v>979</v>
       </c>
       <c r="F356" s="89" t="s">
         <v>13</v>
@@ -18865,7 +18862,7 @@
         <v>617</v>
       </c>
       <c r="E357" s="91" t="s">
-        <v>980</v>
+        <v>979</v>
       </c>
       <c r="F357" s="89" t="s">
         <v>13</v>
@@ -18901,7 +18898,7 @@
         <v>618</v>
       </c>
       <c r="E358" s="91" t="s">
-        <v>980</v>
+        <v>979</v>
       </c>
       <c r="F358" s="89" t="s">
         <v>13</v>
@@ -18937,7 +18934,7 @@
         <v>619</v>
       </c>
       <c r="E359" s="91" t="s">
-        <v>980</v>
+        <v>979</v>
       </c>
       <c r="F359" s="89" t="s">
         <v>13</v>
@@ -18973,7 +18970,7 @@
         <v>620</v>
       </c>
       <c r="E360" s="91" t="s">
-        <v>980</v>
+        <v>979</v>
       </c>
       <c r="F360" s="89" t="s">
         <v>13</v>
@@ -19009,7 +19006,7 @@
         <v>621</v>
       </c>
       <c r="E361" s="91" t="s">
-        <v>980</v>
+        <v>979</v>
       </c>
       <c r="F361" s="89" t="s">
         <v>13</v>
@@ -19045,7 +19042,7 @@
         <v>622</v>
       </c>
       <c r="E362" s="91" t="s">
-        <v>980</v>
+        <v>979</v>
       </c>
       <c r="F362" s="89" t="s">
         <v>13</v>
@@ -19081,7 +19078,7 @@
         <v>623</v>
       </c>
       <c r="E363" s="91" t="s">
-        <v>980</v>
+        <v>979</v>
       </c>
       <c r="F363" s="89" t="s">
         <v>13</v>
@@ -19117,7 +19114,7 @@
         <v>624</v>
       </c>
       <c r="E364" s="91" t="s">
-        <v>980</v>
+        <v>979</v>
       </c>
       <c r="F364" s="89" t="s">
         <v>13</v>
@@ -19153,7 +19150,7 @@
         <v>625</v>
       </c>
       <c r="E365" s="91" t="s">
-        <v>980</v>
+        <v>979</v>
       </c>
       <c r="F365" s="89" t="s">
         <v>13</v>
@@ -19189,7 +19186,7 @@
         <v>626</v>
       </c>
       <c r="E366" s="91" t="s">
-        <v>980</v>
+        <v>979</v>
       </c>
       <c r="F366" s="89" t="s">
         <v>13</v>
@@ -19225,7 +19222,7 @@
         <v>627</v>
       </c>
       <c r="E367" s="91" t="s">
-        <v>980</v>
+        <v>979</v>
       </c>
       <c r="F367" s="89" t="s">
         <v>13</v>
@@ -19261,7 +19258,7 @@
         <v>628</v>
       </c>
       <c r="E368" s="91" t="s">
-        <v>980</v>
+        <v>979</v>
       </c>
       <c r="F368" s="89" t="s">
         <v>13</v>
@@ -19297,7 +19294,7 @@
         <v>629</v>
       </c>
       <c r="E369" s="91" t="s">
-        <v>980</v>
+        <v>979</v>
       </c>
       <c r="F369" s="89" t="s">
         <v>13</v>
@@ -19333,7 +19330,7 @@
         <v>630</v>
       </c>
       <c r="E370" s="91" t="s">
-        <v>980</v>
+        <v>979</v>
       </c>
       <c r="F370" s="89" t="s">
         <v>13</v>
@@ -19369,7 +19366,7 @@
         <v>631</v>
       </c>
       <c r="E371" s="91" t="s">
-        <v>980</v>
+        <v>979</v>
       </c>
       <c r="F371" s="89" t="s">
         <v>13</v>
@@ -19405,7 +19402,7 @@
         <v>632</v>
       </c>
       <c r="E372" s="91" t="s">
-        <v>980</v>
+        <v>979</v>
       </c>
       <c r="F372" s="89" t="s">
         <v>13</v>
@@ -19441,7 +19438,7 @@
         <v>633</v>
       </c>
       <c r="E373" s="91" t="s">
-        <v>980</v>
+        <v>979</v>
       </c>
       <c r="F373" s="89" t="s">
         <v>13</v>
@@ -19477,7 +19474,7 @@
         <v>596</v>
       </c>
       <c r="E374" s="91" t="s">
-        <v>980</v>
+        <v>979</v>
       </c>
       <c r="F374" s="89" t="s">
         <v>13</v>
@@ -19513,7 +19510,7 @@
         <v>634</v>
       </c>
       <c r="E375" s="91" t="s">
-        <v>980</v>
+        <v>979</v>
       </c>
       <c r="F375" s="89" t="s">
         <v>13</v>
@@ -19549,7 +19546,7 @@
         <v>635</v>
       </c>
       <c r="E376" s="91" t="s">
-        <v>980</v>
+        <v>979</v>
       </c>
       <c r="F376" s="89" t="s">
         <v>13</v>
@@ -19585,7 +19582,7 @@
         <v>636</v>
       </c>
       <c r="E377" s="91" t="s">
-        <v>980</v>
+        <v>979</v>
       </c>
       <c r="F377" s="89" t="s">
         <v>13</v>
@@ -19621,7 +19618,7 @@
         <v>637</v>
       </c>
       <c r="E378" s="91" t="s">
-        <v>980</v>
+        <v>979</v>
       </c>
       <c r="F378" s="89" t="s">
         <v>13</v>
@@ -19657,7 +19654,7 @@
         <v>638</v>
       </c>
       <c r="E379" s="91" t="s">
-        <v>980</v>
+        <v>979</v>
       </c>
       <c r="F379" s="89" t="s">
         <v>13</v>
@@ -19693,7 +19690,7 @@
         <v>639</v>
       </c>
       <c r="E380" s="91" t="s">
-        <v>980</v>
+        <v>979</v>
       </c>
       <c r="F380" s="89" t="s">
         <v>13</v>
@@ -19729,7 +19726,7 @@
         <v>640</v>
       </c>
       <c r="E381" s="91" t="s">
-        <v>980</v>
+        <v>979</v>
       </c>
       <c r="F381" s="89" t="s">
         <v>13</v>
@@ -19765,7 +19762,7 @@
         <v>641</v>
       </c>
       <c r="E382" s="91" t="s">
-        <v>980</v>
+        <v>979</v>
       </c>
       <c r="F382" s="89" t="s">
         <v>13</v>
@@ -19801,7 +19798,7 @@
         <v>642</v>
       </c>
       <c r="E383" s="91" t="s">
-        <v>980</v>
+        <v>979</v>
       </c>
       <c r="F383" s="89" t="s">
         <v>13</v>
@@ -19837,7 +19834,7 @@
         <v>643</v>
       </c>
       <c r="E384" s="91" t="s">
-        <v>980</v>
+        <v>979</v>
       </c>
       <c r="F384" s="89" t="s">
         <v>13</v>
@@ -19873,7 +19870,7 @@
         <v>644</v>
       </c>
       <c r="E385" s="91" t="s">
-        <v>980</v>
+        <v>979</v>
       </c>
       <c r="F385" s="89" t="s">
         <v>13</v>
@@ -19909,7 +19906,7 @@
         <v>645</v>
       </c>
       <c r="E386" s="91" t="s">
-        <v>980</v>
+        <v>979</v>
       </c>
       <c r="F386" s="89" t="s">
         <v>13</v>
@@ -19945,7 +19942,7 @@
         <v>646</v>
       </c>
       <c r="E387" s="91" t="s">
-        <v>980</v>
+        <v>979</v>
       </c>
       <c r="F387" s="89" t="s">
         <v>13</v>
@@ -19981,7 +19978,7 @@
         <v>647</v>
       </c>
       <c r="E388" s="91" t="s">
-        <v>980</v>
+        <v>979</v>
       </c>
       <c r="F388" s="89" t="s">
         <v>13</v>
@@ -20017,7 +20014,7 @@
         <v>648</v>
       </c>
       <c r="E389" s="91" t="s">
-        <v>980</v>
+        <v>979</v>
       </c>
       <c r="F389" s="89" t="s">
         <v>13</v>
@@ -20053,7 +20050,7 @@
         <v>649</v>
       </c>
       <c r="E390" s="91" t="s">
-        <v>980</v>
+        <v>979</v>
       </c>
       <c r="F390" s="89" t="s">
         <v>13</v>
@@ -20089,7 +20086,7 @@
         <v>650</v>
       </c>
       <c r="E391" s="91" t="s">
-        <v>980</v>
+        <v>979</v>
       </c>
       <c r="F391" s="89" t="s">
         <v>13</v>
@@ -20125,7 +20122,7 @@
         <v>651</v>
       </c>
       <c r="E392" s="91" t="s">
-        <v>980</v>
+        <v>979</v>
       </c>
       <c r="F392" s="89" t="s">
         <v>13</v>
@@ -20161,7 +20158,7 @@
         <v>652</v>
       </c>
       <c r="E393" s="91" t="s">
-        <v>980</v>
+        <v>979</v>
       </c>
       <c r="F393" s="89" t="s">
         <v>13</v>
@@ -20197,7 +20194,7 @@
         <v>653</v>
       </c>
       <c r="E394" s="91" t="s">
-        <v>980</v>
+        <v>979</v>
       </c>
       <c r="F394" s="89" t="s">
         <v>13</v>
@@ -20233,7 +20230,7 @@
         <v>654</v>
       </c>
       <c r="E395" s="91" t="s">
-        <v>980</v>
+        <v>979</v>
       </c>
       <c r="F395" s="89" t="s">
         <v>13</v>
@@ -20269,7 +20266,7 @@
         <v>655</v>
       </c>
       <c r="E396" s="91" t="s">
-        <v>980</v>
+        <v>979</v>
       </c>
       <c r="F396" s="89" t="s">
         <v>13</v>
@@ -20305,7 +20302,7 @@
         <v>656</v>
       </c>
       <c r="E397" s="91" t="s">
-        <v>980</v>
+        <v>979</v>
       </c>
       <c r="F397" s="89" t="s">
         <v>13</v>
@@ -20341,7 +20338,7 @@
         <v>657</v>
       </c>
       <c r="E398" s="91" t="s">
-        <v>980</v>
+        <v>979</v>
       </c>
       <c r="F398" s="89" t="s">
         <v>13</v>
@@ -20377,7 +20374,7 @@
         <v>658</v>
       </c>
       <c r="E399" s="91" t="s">
-        <v>980</v>
+        <v>979</v>
       </c>
       <c r="F399" s="89" t="s">
         <v>13</v>
@@ -20413,7 +20410,7 @@
         <v>244</v>
       </c>
       <c r="E400" s="91" t="s">
-        <v>980</v>
+        <v>979</v>
       </c>
       <c r="F400" s="89" t="s">
         <v>13</v>
@@ -20449,7 +20446,7 @@
         <v>659</v>
       </c>
       <c r="E401" s="91" t="s">
-        <v>980</v>
+        <v>979</v>
       </c>
       <c r="F401" s="89" t="s">
         <v>13</v>
@@ -20485,7 +20482,7 @@
         <v>660</v>
       </c>
       <c r="E402" s="91" t="s">
-        <v>980</v>
+        <v>979</v>
       </c>
       <c r="F402" s="89" t="s">
         <v>13</v>
@@ -20521,7 +20518,7 @@
         <v>661</v>
       </c>
       <c r="E403" s="91" t="s">
-        <v>980</v>
+        <v>979</v>
       </c>
       <c r="F403" s="89" t="s">
         <v>13</v>
@@ -20557,7 +20554,7 @@
         <v>566</v>
       </c>
       <c r="E404" s="91" t="s">
-        <v>980</v>
+        <v>979</v>
       </c>
       <c r="F404" s="89" t="s">
         <v>13</v>
@@ -20593,7 +20590,7 @@
         <v>662</v>
       </c>
       <c r="E405" s="91" t="s">
-        <v>980</v>
+        <v>979</v>
       </c>
       <c r="F405" s="89" t="s">
         <v>13</v>
@@ -20629,7 +20626,7 @@
         <v>663</v>
       </c>
       <c r="E406" s="91" t="s">
-        <v>980</v>
+        <v>979</v>
       </c>
       <c r="F406" s="89" t="s">
         <v>13</v>
@@ -20665,7 +20662,7 @@
         <v>664</v>
       </c>
       <c r="E407" s="91" t="s">
-        <v>980</v>
+        <v>979</v>
       </c>
       <c r="F407" s="89" t="s">
         <v>13</v>
@@ -20701,7 +20698,7 @@
         <v>665</v>
       </c>
       <c r="E408" s="91" t="s">
-        <v>980</v>
+        <v>979</v>
       </c>
       <c r="F408" s="89" t="s">
         <v>13</v>
@@ -20737,7 +20734,7 @@
         <v>666</v>
       </c>
       <c r="E409" s="91" t="s">
-        <v>980</v>
+        <v>979</v>
       </c>
       <c r="F409" s="89" t="s">
         <v>13</v>
@@ -20773,7 +20770,7 @@
         <v>667</v>
       </c>
       <c r="E410" s="91" t="s">
-        <v>980</v>
+        <v>979</v>
       </c>
       <c r="F410" s="89" t="s">
         <v>13</v>
@@ -20809,7 +20806,7 @@
         <v>668</v>
       </c>
       <c r="E411" s="91" t="s">
-        <v>980</v>
+        <v>979</v>
       </c>
       <c r="F411" s="89" t="s">
         <v>13</v>
@@ -20845,7 +20842,7 @@
         <v>669</v>
       </c>
       <c r="E412" s="91" t="s">
-        <v>980</v>
+        <v>979</v>
       </c>
       <c r="F412" s="89" t="s">
         <v>13</v>
@@ -20881,7 +20878,7 @@
         <v>670</v>
       </c>
       <c r="E413" s="91" t="s">
-        <v>980</v>
+        <v>979</v>
       </c>
       <c r="F413" s="89" t="s">
         <v>13</v>
@@ -20917,7 +20914,7 @@
         <v>671</v>
       </c>
       <c r="E414" s="91" t="s">
-        <v>980</v>
+        <v>979</v>
       </c>
       <c r="F414" s="89" t="s">
         <v>13</v>
@@ -20953,7 +20950,7 @@
         <v>672</v>
       </c>
       <c r="E415" s="91" t="s">
-        <v>980</v>
+        <v>979</v>
       </c>
       <c r="F415" s="89" t="s">
         <v>13</v>
@@ -20989,7 +20986,7 @@
         <v>673</v>
       </c>
       <c r="E416" s="91" t="s">
-        <v>980</v>
+        <v>979</v>
       </c>
       <c r="F416" s="89" t="s">
         <v>13</v>
@@ -21025,7 +21022,7 @@
         <v>674</v>
       </c>
       <c r="E417" s="91" t="s">
-        <v>980</v>
+        <v>979</v>
       </c>
       <c r="F417" s="89" t="s">
         <v>13</v>
@@ -21061,7 +21058,7 @@
         <v>675</v>
       </c>
       <c r="E418" s="91" t="s">
-        <v>980</v>
+        <v>979</v>
       </c>
       <c r="F418" s="89" t="s">
         <v>13</v>
@@ -21097,7 +21094,7 @@
         <v>676</v>
       </c>
       <c r="E419" s="91" t="s">
-        <v>980</v>
+        <v>979</v>
       </c>
       <c r="F419" s="89" t="s">
         <v>13</v>
@@ -21133,7 +21130,7 @@
         <v>677</v>
       </c>
       <c r="E420" s="91" t="s">
-        <v>980</v>
+        <v>979</v>
       </c>
       <c r="F420" s="89" t="s">
         <v>13</v>
@@ -21169,7 +21166,7 @@
         <v>678</v>
       </c>
       <c r="E421" s="91" t="s">
-        <v>980</v>
+        <v>979</v>
       </c>
       <c r="F421" s="89" t="s">
         <v>13</v>
@@ -21205,7 +21202,7 @@
         <v>679</v>
       </c>
       <c r="E422" s="91" t="s">
-        <v>980</v>
+        <v>979</v>
       </c>
       <c r="F422" s="89" t="s">
         <v>13</v>
@@ -21241,7 +21238,7 @@
         <v>680</v>
       </c>
       <c r="E423" s="91" t="s">
-        <v>980</v>
+        <v>979</v>
       </c>
       <c r="F423" s="89" t="s">
         <v>13</v>
@@ -21277,7 +21274,7 @@
         <v>681</v>
       </c>
       <c r="E424" s="91" t="s">
-        <v>980</v>
+        <v>979</v>
       </c>
       <c r="F424" s="89" t="s">
         <v>13</v>
@@ -21313,7 +21310,7 @@
         <v>682</v>
       </c>
       <c r="E425" s="91" t="s">
-        <v>980</v>
+        <v>979</v>
       </c>
       <c r="F425" s="89" t="s">
         <v>13</v>
@@ -21349,7 +21346,7 @@
         <v>683</v>
       </c>
       <c r="E426" s="91" t="s">
-        <v>980</v>
+        <v>979</v>
       </c>
       <c r="F426" s="89" t="s">
         <v>13</v>
@@ -21385,7 +21382,7 @@
         <v>684</v>
       </c>
       <c r="E427" s="91" t="s">
-        <v>980</v>
+        <v>979</v>
       </c>
       <c r="F427" s="89" t="s">
         <v>13</v>
@@ -21421,7 +21418,7 @@
         <v>685</v>
       </c>
       <c r="E428" s="91" t="s">
-        <v>980</v>
+        <v>979</v>
       </c>
       <c r="F428" s="89" t="s">
         <v>13</v>
@@ -21457,7 +21454,7 @@
         <v>686</v>
       </c>
       <c r="E429" s="91" t="s">
-        <v>980</v>
+        <v>979</v>
       </c>
       <c r="F429" s="89" t="s">
         <v>13</v>
@@ -21493,7 +21490,7 @@
         <v>687</v>
       </c>
       <c r="E430" s="91" t="s">
-        <v>980</v>
+        <v>979</v>
       </c>
       <c r="F430" s="89" t="s">
         <v>13</v>
@@ -21529,7 +21526,7 @@
         <v>688</v>
       </c>
       <c r="E431" s="91" t="s">
-        <v>980</v>
+        <v>979</v>
       </c>
       <c r="F431" s="89" t="s">
         <v>13</v>
@@ -21565,7 +21562,7 @@
         <v>689</v>
       </c>
       <c r="E432" s="91" t="s">
-        <v>980</v>
+        <v>979</v>
       </c>
       <c r="F432" s="89" t="s">
         <v>13</v>
@@ -21601,7 +21598,7 @@
         <v>690</v>
       </c>
       <c r="E433" s="91" t="s">
-        <v>980</v>
+        <v>979</v>
       </c>
       <c r="F433" s="89" t="s">
         <v>13</v>
@@ -21637,7 +21634,7 @@
         <v>691</v>
       </c>
       <c r="E434" s="91" t="s">
-        <v>980</v>
+        <v>979</v>
       </c>
       <c r="F434" s="89" t="s">
         <v>13</v>
@@ -21673,7 +21670,7 @@
         <v>213</v>
       </c>
       <c r="E435" s="91" t="s">
-        <v>980</v>
+        <v>979</v>
       </c>
       <c r="F435" s="89" t="s">
         <v>13</v>
@@ -21709,7 +21706,7 @@
         <v>692</v>
       </c>
       <c r="E436" s="91" t="s">
-        <v>980</v>
+        <v>979</v>
       </c>
       <c r="F436" s="89" t="s">
         <v>13</v>
@@ -21745,7 +21742,7 @@
         <v>693</v>
       </c>
       <c r="E437" s="91" t="s">
-        <v>980</v>
+        <v>979</v>
       </c>
       <c r="F437" s="89" t="s">
         <v>13</v>
@@ -21781,7 +21778,7 @@
         <v>694</v>
       </c>
       <c r="E438" s="91" t="s">
-        <v>980</v>
+        <v>979</v>
       </c>
       <c r="F438" s="89" t="s">
         <v>13</v>
@@ -21817,7 +21814,7 @@
         <v>695</v>
       </c>
       <c r="E439" s="91" t="s">
-        <v>980</v>
+        <v>979</v>
       </c>
       <c r="F439" s="89" t="s">
         <v>13</v>
@@ -21853,7 +21850,7 @@
         <v>696</v>
       </c>
       <c r="E440" s="91" t="s">
-        <v>980</v>
+        <v>979</v>
       </c>
       <c r="F440" s="89" t="s">
         <v>13</v>
@@ -21889,7 +21886,7 @@
         <v>216</v>
       </c>
       <c r="E441" s="91" t="s">
-        <v>980</v>
+        <v>979</v>
       </c>
       <c r="F441" s="89" t="s">
         <v>13</v>
@@ -21925,7 +21922,7 @@
         <v>697</v>
       </c>
       <c r="E442" s="91" t="s">
-        <v>980</v>
+        <v>979</v>
       </c>
       <c r="F442" s="89" t="s">
         <v>13</v>
@@ -21961,7 +21958,7 @@
         <v>698</v>
       </c>
       <c r="E443" s="91" t="s">
-        <v>980</v>
+        <v>979</v>
       </c>
       <c r="F443" s="89" t="s">
         <v>13</v>
@@ -21997,7 +21994,7 @@
         <v>699</v>
       </c>
       <c r="E444" s="91" t="s">
-        <v>980</v>
+        <v>979</v>
       </c>
       <c r="F444" s="89" t="s">
         <v>13</v>
@@ -22033,7 +22030,7 @@
         <v>700</v>
       </c>
       <c r="E445" s="91" t="s">
-        <v>980</v>
+        <v>979</v>
       </c>
       <c r="F445" s="89" t="s">
         <v>13</v>
@@ -22069,7 +22066,7 @@
         <v>701</v>
       </c>
       <c r="E446" s="91" t="s">
-        <v>980</v>
+        <v>979</v>
       </c>
       <c r="F446" s="89" t="s">
         <v>13</v>
@@ -22105,7 +22102,7 @@
         <v>702</v>
       </c>
       <c r="E447" s="91" t="s">
-        <v>980</v>
+        <v>979</v>
       </c>
       <c r="F447" s="89" t="s">
         <v>13</v>
@@ -22141,7 +22138,7 @@
         <v>703</v>
       </c>
       <c r="E448" s="91" t="s">
-        <v>980</v>
+        <v>979</v>
       </c>
       <c r="F448" s="89" t="s">
         <v>13</v>
@@ -22177,7 +22174,7 @@
         <v>704</v>
       </c>
       <c r="E449" s="91" t="s">
-        <v>980</v>
+        <v>979</v>
       </c>
       <c r="F449" s="89" t="s">
         <v>13</v>
@@ -22213,7 +22210,7 @@
         <v>705</v>
       </c>
       <c r="E450" s="91" t="s">
-        <v>980</v>
+        <v>979</v>
       </c>
       <c r="F450" s="89" t="s">
         <v>13</v>
@@ -22249,7 +22246,7 @@
         <v>706</v>
       </c>
       <c r="E451" s="91" t="s">
-        <v>980</v>
+        <v>979</v>
       </c>
       <c r="F451" s="89" t="s">
         <v>13</v>
@@ -22285,7 +22282,7 @@
         <v>707</v>
       </c>
       <c r="E452" s="91" t="s">
-        <v>980</v>
+        <v>979</v>
       </c>
       <c r="F452" s="89" t="s">
         <v>13</v>
@@ -22321,7 +22318,7 @@
         <v>708</v>
       </c>
       <c r="E453" s="91" t="s">
-        <v>980</v>
+        <v>979</v>
       </c>
       <c r="F453" s="89" t="s">
         <v>13</v>
@@ -22357,7 +22354,7 @@
         <v>709</v>
       </c>
       <c r="E454" s="91" t="s">
-        <v>980</v>
+        <v>979</v>
       </c>
       <c r="F454" s="89" t="s">
         <v>13</v>
@@ -22393,7 +22390,7 @@
         <v>710</v>
       </c>
       <c r="E455" s="91" t="s">
-        <v>980</v>
+        <v>979</v>
       </c>
       <c r="F455" s="89" t="s">
         <v>13</v>
@@ -22429,7 +22426,7 @@
         <v>711</v>
       </c>
       <c r="E456" s="91" t="s">
-        <v>980</v>
+        <v>979</v>
       </c>
       <c r="F456" s="89" t="s">
         <v>13</v>
@@ -22465,7 +22462,7 @@
         <v>712</v>
       </c>
       <c r="E457" s="91" t="s">
-        <v>980</v>
+        <v>979</v>
       </c>
       <c r="F457" s="89" t="s">
         <v>13</v>
@@ -22501,7 +22498,7 @@
         <v>713</v>
       </c>
       <c r="E458" s="91" t="s">
-        <v>980</v>
+        <v>979</v>
       </c>
       <c r="F458" s="89" t="s">
         <v>13</v>
@@ -22537,7 +22534,7 @@
         <v>714</v>
       </c>
       <c r="E459" s="91" t="s">
-        <v>980</v>
+        <v>979</v>
       </c>
       <c r="F459" s="89" t="s">
         <v>13</v>
@@ -22573,7 +22570,7 @@
         <v>715</v>
       </c>
       <c r="E460" s="91" t="s">
-        <v>980</v>
+        <v>979</v>
       </c>
       <c r="F460" s="89" t="s">
         <v>13</v>
@@ -22609,7 +22606,7 @@
         <v>716</v>
       </c>
       <c r="E461" s="91" t="s">
-        <v>980</v>
+        <v>979</v>
       </c>
       <c r="F461" s="89" t="s">
         <v>13</v>
@@ -22645,7 +22642,7 @@
         <v>717</v>
       </c>
       <c r="E462" s="91" t="s">
-        <v>980</v>
+        <v>979</v>
       </c>
       <c r="F462" s="89" t="s">
         <v>13</v>
@@ -22681,7 +22678,7 @@
         <v>181</v>
       </c>
       <c r="E463" s="91" t="s">
-        <v>980</v>
+        <v>979</v>
       </c>
       <c r="F463" s="89" t="s">
         <v>13</v>
@@ -22717,7 +22714,7 @@
         <v>718</v>
       </c>
       <c r="E464" s="91" t="s">
-        <v>980</v>
+        <v>979</v>
       </c>
       <c r="F464" s="89" t="s">
         <v>13</v>
@@ -22753,7 +22750,7 @@
         <v>719</v>
       </c>
       <c r="E465" s="91" t="s">
-        <v>980</v>
+        <v>979</v>
       </c>
       <c r="F465" s="89" t="s">
         <v>13</v>
@@ -22789,7 +22786,7 @@
         <v>720</v>
       </c>
       <c r="E466" s="91" t="s">
-        <v>980</v>
+        <v>979</v>
       </c>
       <c r="F466" s="89" t="s">
         <v>13</v>
@@ -22825,7 +22822,7 @@
         <v>721</v>
       </c>
       <c r="E467" s="91" t="s">
-        <v>980</v>
+        <v>979</v>
       </c>
       <c r="F467" s="89" t="s">
         <v>13</v>
@@ -22861,7 +22858,7 @@
         <v>722</v>
       </c>
       <c r="E468" s="91" t="s">
-        <v>980</v>
+        <v>979</v>
       </c>
       <c r="F468" s="89" t="s">
         <v>13</v>
@@ -22897,7 +22894,7 @@
         <v>204</v>
       </c>
       <c r="E469" s="91" t="s">
-        <v>980</v>
+        <v>979</v>
       </c>
       <c r="F469" s="89" t="s">
         <v>13</v>
@@ -22933,7 +22930,7 @@
         <v>723</v>
       </c>
       <c r="E470" s="91" t="s">
-        <v>980</v>
+        <v>979</v>
       </c>
       <c r="F470" s="89" t="s">
         <v>13</v>
@@ -22969,7 +22966,7 @@
         <v>724</v>
       </c>
       <c r="E471" s="91" t="s">
-        <v>980</v>
+        <v>979</v>
       </c>
       <c r="F471" s="89" t="s">
         <v>13</v>
@@ -23005,7 +23002,7 @@
         <v>860</v>
       </c>
       <c r="E472" s="91" t="s">
-        <v>980</v>
+        <v>979</v>
       </c>
       <c r="F472" s="89" t="s">
         <v>13</v>
@@ -23015,7 +23012,7 @@
       </c>
       <c r="H472" s="66"/>
       <c r="I472" s="86" t="s">
-        <v>974</v>
+        <v>995</v>
       </c>
       <c r="J472" s="86" t="s">
         <v>970</v>
@@ -23043,7 +23040,7 @@
         <v>861</v>
       </c>
       <c r="E473" s="91" t="s">
-        <v>980</v>
+        <v>979</v>
       </c>
       <c r="F473" s="89" t="s">
         <v>13</v>
@@ -23053,7 +23050,7 @@
       </c>
       <c r="H473" s="66"/>
       <c r="I473" s="86" t="s">
-        <v>974</v>
+        <v>995</v>
       </c>
       <c r="J473" s="86" t="s">
         <v>970</v>
@@ -23081,7 +23078,7 @@
         <v>284</v>
       </c>
       <c r="E474" s="91" t="s">
-        <v>980</v>
+        <v>979</v>
       </c>
       <c r="F474" s="89" t="s">
         <v>13</v>
@@ -23091,7 +23088,7 @@
       </c>
       <c r="H474" s="66"/>
       <c r="I474" s="86" t="s">
-        <v>995</v>
+        <v>994</v>
       </c>
       <c r="J474" s="86" t="s">
         <v>970</v>
@@ -23109,7 +23106,7 @@
         <v>16.53</v>
       </c>
       <c r="Q474" s="62" t="s">
-        <v>994</v>
+        <v>992</v>
       </c>
     </row>
     <row r="475" spans="1:17" x14ac:dyDescent="0.55000000000000004">
@@ -23124,7 +23121,7 @@
         <v>195</v>
       </c>
       <c r="E475" s="91" t="s">
-        <v>980</v>
+        <v>979</v>
       </c>
       <c r="F475" s="89" t="s">
         <v>13</v>
@@ -23134,7 +23131,7 @@
       </c>
       <c r="H475" s="66"/>
       <c r="I475" s="86" t="s">
-        <v>995</v>
+        <v>994</v>
       </c>
       <c r="J475" s="86" t="s">
         <v>970</v>
@@ -23152,7 +23149,7 @@
         <v>33.29</v>
       </c>
       <c r="Q475" s="62" t="s">
-        <v>994</v>
+        <v>992</v>
       </c>
     </row>
     <row r="476" spans="1:17" x14ac:dyDescent="0.55000000000000004">
@@ -23167,7 +23164,7 @@
         <v>775</v>
       </c>
       <c r="E476" s="91" t="s">
-        <v>980</v>
+        <v>979</v>
       </c>
       <c r="F476" s="88" t="s">
         <v>13</v>
@@ -23205,7 +23202,7 @@
         <v>305</v>
       </c>
       <c r="E477" s="91" t="s">
-        <v>980</v>
+        <v>979</v>
       </c>
       <c r="F477" s="89" t="s">
         <v>13</v>
@@ -23215,7 +23212,7 @@
       </c>
       <c r="H477" s="66"/>
       <c r="I477" s="86" t="s">
-        <v>995</v>
+        <v>994</v>
       </c>
       <c r="J477" s="86" t="s">
         <v>970</v>
@@ -23233,7 +23230,7 @@
         <v>411.84</v>
       </c>
       <c r="Q477" s="62" t="s">
-        <v>994</v>
+        <v>992</v>
       </c>
     </row>
     <row r="478" spans="1:17" x14ac:dyDescent="0.55000000000000004">
@@ -23248,7 +23245,7 @@
         <v>729</v>
       </c>
       <c r="E478" s="91" t="s">
-        <v>980</v>
+        <v>979</v>
       </c>
       <c r="F478" s="89" t="s">
         <v>13</v>
@@ -23258,7 +23255,7 @@
       </c>
       <c r="H478" s="66"/>
       <c r="I478" s="86" t="s">
-        <v>995</v>
+        <v>994</v>
       </c>
       <c r="J478" s="86" t="s">
         <v>970</v>
@@ -23276,7 +23273,7 @@
         <v>7.56</v>
       </c>
       <c r="Q478" s="62" t="s">
-        <v>994</v>
+        <v>992</v>
       </c>
     </row>
     <row r="479" spans="1:17" x14ac:dyDescent="0.55000000000000004">
@@ -23291,7 +23288,7 @@
         <v>153</v>
       </c>
       <c r="E479" s="91" t="s">
-        <v>980</v>
+        <v>979</v>
       </c>
       <c r="F479" s="89" t="s">
         <v>13</v>
@@ -23301,7 +23298,7 @@
       </c>
       <c r="H479" s="66"/>
       <c r="I479" s="86" t="s">
-        <v>995</v>
+        <v>994</v>
       </c>
       <c r="J479" s="86" t="s">
         <v>970</v>
@@ -23319,7 +23316,7 @@
         <v>6.07</v>
       </c>
       <c r="Q479" s="62" t="s">
-        <v>994</v>
+        <v>992</v>
       </c>
     </row>
     <row r="480" spans="1:17" x14ac:dyDescent="0.55000000000000004">
@@ -23334,7 +23331,7 @@
         <v>730</v>
       </c>
       <c r="E480" s="91" t="s">
-        <v>980</v>
+        <v>979</v>
       </c>
       <c r="F480" s="89" t="s">
         <v>13</v>
@@ -23344,7 +23341,7 @@
       </c>
       <c r="H480" s="66"/>
       <c r="I480" s="86" t="s">
-        <v>995</v>
+        <v>994</v>
       </c>
       <c r="J480" s="86" t="s">
         <v>970</v>
@@ -23362,7 +23359,7 @@
         <v>109.93</v>
       </c>
       <c r="Q480" s="62" t="s">
-        <v>994</v>
+        <v>992</v>
       </c>
     </row>
     <row r="481" spans="1:17" x14ac:dyDescent="0.55000000000000004">
@@ -23377,7 +23374,7 @@
         <v>314</v>
       </c>
       <c r="E481" s="91" t="s">
-        <v>980</v>
+        <v>979</v>
       </c>
       <c r="F481" s="89" t="s">
         <v>13</v>
@@ -23387,7 +23384,7 @@
       </c>
       <c r="H481" s="66"/>
       <c r="I481" s="86" t="s">
-        <v>995</v>
+        <v>994</v>
       </c>
       <c r="J481" s="86" t="s">
         <v>970</v>
@@ -23405,7 +23402,7 @@
         <v>76.12</v>
       </c>
       <c r="Q481" s="62" t="s">
-        <v>994</v>
+        <v>992</v>
       </c>
     </row>
     <row r="482" spans="1:17" x14ac:dyDescent="0.55000000000000004">
@@ -23420,7 +23417,7 @@
         <v>731</v>
       </c>
       <c r="E482" s="91" t="s">
-        <v>980</v>
+        <v>979</v>
       </c>
       <c r="F482" s="89" t="s">
         <v>13</v>
@@ -23430,7 +23427,7 @@
       </c>
       <c r="H482" s="66"/>
       <c r="I482" s="86" t="s">
-        <v>995</v>
+        <v>994</v>
       </c>
       <c r="J482" s="86" t="s">
         <v>970</v>
@@ -23448,7 +23445,7 @@
         <v>27.23</v>
       </c>
       <c r="Q482" s="62" t="s">
-        <v>994</v>
+        <v>992</v>
       </c>
     </row>
     <row r="483" spans="1:17" x14ac:dyDescent="0.55000000000000004">
@@ -23463,7 +23460,7 @@
         <v>145</v>
       </c>
       <c r="E483" s="91" t="s">
-        <v>980</v>
+        <v>979</v>
       </c>
       <c r="F483" s="89" t="s">
         <v>13</v>
@@ -23473,7 +23470,7 @@
       </c>
       <c r="H483" s="66"/>
       <c r="I483" s="86" t="s">
-        <v>995</v>
+        <v>994</v>
       </c>
       <c r="J483" s="86" t="s">
         <v>970</v>
@@ -23491,7 +23488,7 @@
         <v>48.73</v>
       </c>
       <c r="Q483" s="62" t="s">
-        <v>994</v>
+        <v>992</v>
       </c>
     </row>
     <row r="484" spans="1:17" x14ac:dyDescent="0.55000000000000004">
@@ -23506,7 +23503,7 @@
         <v>542</v>
       </c>
       <c r="E484" s="91" t="s">
-        <v>980</v>
+        <v>979</v>
       </c>
       <c r="F484" s="89" t="s">
         <v>13</v>
@@ -23516,7 +23513,7 @@
       </c>
       <c r="H484" s="66"/>
       <c r="I484" s="86" t="s">
-        <v>995</v>
+        <v>994</v>
       </c>
       <c r="J484" s="86" t="s">
         <v>970</v>
@@ -23534,7 +23531,7 @@
         <v>16.329999999999998</v>
       </c>
       <c r="Q484" s="62" t="s">
-        <v>994</v>
+        <v>992</v>
       </c>
     </row>
     <row r="485" spans="1:17" x14ac:dyDescent="0.55000000000000004">
@@ -23549,7 +23546,7 @@
         <v>543</v>
       </c>
       <c r="E485" s="91" t="s">
-        <v>980</v>
+        <v>979</v>
       </c>
       <c r="F485" s="89" t="s">
         <v>13</v>
@@ -23559,7 +23556,7 @@
       </c>
       <c r="H485" s="66"/>
       <c r="I485" s="86" t="s">
-        <v>995</v>
+        <v>994</v>
       </c>
       <c r="J485" s="86" t="s">
         <v>970</v>
@@ -23577,7 +23574,7 @@
         <v>21.98</v>
       </c>
       <c r="Q485" s="62" t="s">
-        <v>994</v>
+        <v>992</v>
       </c>
     </row>
     <row r="486" spans="1:17" x14ac:dyDescent="0.55000000000000004">
@@ -23592,7 +23589,7 @@
         <v>544</v>
       </c>
       <c r="E486" s="91" t="s">
-        <v>980</v>
+        <v>979</v>
       </c>
       <c r="F486" s="89" t="s">
         <v>13</v>
@@ -23602,7 +23599,7 @@
       </c>
       <c r="H486" s="66"/>
       <c r="I486" s="86" t="s">
-        <v>995</v>
+        <v>994</v>
       </c>
       <c r="J486" s="86" t="s">
         <v>970</v>
@@ -23620,7 +23617,7 @@
         <v>16.53</v>
       </c>
       <c r="Q486" s="62" t="s">
-        <v>994</v>
+        <v>992</v>
       </c>
     </row>
     <row r="487" spans="1:17" x14ac:dyDescent="0.55000000000000004">
@@ -23635,7 +23632,7 @@
         <v>282</v>
       </c>
       <c r="E487" s="91" t="s">
-        <v>980</v>
+        <v>979</v>
       </c>
       <c r="F487" s="89" t="s">
         <v>13</v>
@@ -23645,7 +23642,7 @@
       </c>
       <c r="H487" s="66"/>
       <c r="I487" s="86" t="s">
-        <v>995</v>
+        <v>994</v>
       </c>
       <c r="J487" s="86" t="s">
         <v>970</v>
@@ -23663,7 +23660,7 @@
         <v>11.66</v>
       </c>
       <c r="Q487" s="62" t="s">
-        <v>994</v>
+        <v>992</v>
       </c>
     </row>
     <row r="488" spans="1:17" x14ac:dyDescent="0.55000000000000004">
@@ -23678,7 +23675,7 @@
         <v>287</v>
       </c>
       <c r="E488" s="91" t="s">
-        <v>980</v>
+        <v>979</v>
       </c>
       <c r="F488" s="89" t="s">
         <v>13</v>
@@ -23688,7 +23685,7 @@
       </c>
       <c r="H488" s="66"/>
       <c r="I488" s="86" t="s">
-        <v>995</v>
+        <v>994</v>
       </c>
       <c r="J488" s="86" t="s">
         <v>970</v>
@@ -23706,7 +23703,7 @@
         <v>12.41</v>
       </c>
       <c r="Q488" s="62" t="s">
-        <v>994</v>
+        <v>992</v>
       </c>
     </row>
     <row r="489" spans="1:17" x14ac:dyDescent="0.55000000000000004">
@@ -23721,7 +23718,7 @@
         <v>725</v>
       </c>
       <c r="E489" s="91" t="s">
-        <v>980</v>
+        <v>979</v>
       </c>
       <c r="F489" s="89" t="s">
         <v>13</v>
@@ -23759,7 +23756,7 @@
         <v>726</v>
       </c>
       <c r="E490" s="91" t="s">
-        <v>980</v>
+        <v>979</v>
       </c>
       <c r="F490" s="89" t="s">
         <v>13</v>
@@ -23797,7 +23794,7 @@
         <v>545</v>
       </c>
       <c r="E491" s="91" t="s">
-        <v>980</v>
+        <v>979</v>
       </c>
       <c r="F491" s="89" t="s">
         <v>13</v>
@@ -23807,7 +23804,7 @@
       </c>
       <c r="H491" s="66"/>
       <c r="I491" s="86" t="s">
-        <v>995</v>
+        <v>994</v>
       </c>
       <c r="J491" s="86" t="s">
         <v>970</v>
@@ -23825,7 +23822,7 @@
         <v>17.649999999999999</v>
       </c>
       <c r="Q491" s="62" t="s">
-        <v>994</v>
+        <v>992</v>
       </c>
     </row>
     <row r="492" spans="1:17" x14ac:dyDescent="0.55000000000000004">
@@ -23840,7 +23837,7 @@
         <v>871</v>
       </c>
       <c r="E492" s="91" t="s">
-        <v>980</v>
+        <v>979</v>
       </c>
       <c r="F492" s="89" t="s">
         <v>13</v>
@@ -23850,7 +23847,7 @@
       </c>
       <c r="H492" s="66"/>
       <c r="I492" s="86" t="s">
-        <v>995</v>
+        <v>994</v>
       </c>
       <c r="J492" s="86" t="s">
         <v>970</v>
@@ -23868,7 +23865,7 @@
         <v>6.65</v>
       </c>
       <c r="Q492" s="62" t="s">
-        <v>994</v>
+        <v>992</v>
       </c>
     </row>
     <row r="493" spans="1:17" x14ac:dyDescent="0.55000000000000004">
@@ -23883,7 +23880,7 @@
         <v>872</v>
       </c>
       <c r="E493" s="91" t="s">
-        <v>980</v>
+        <v>979</v>
       </c>
       <c r="F493" s="89" t="s">
         <v>13</v>
@@ -23921,7 +23918,7 @@
         <v>794</v>
       </c>
       <c r="E494" s="91" t="s">
-        <v>980</v>
+        <v>979</v>
       </c>
       <c r="F494" s="89" t="s">
         <v>13</v>
@@ -23931,7 +23928,7 @@
       </c>
       <c r="H494" s="66"/>
       <c r="I494" s="86" t="s">
-        <v>995</v>
+        <v>994</v>
       </c>
       <c r="J494" s="86" t="s">
         <v>970</v>
@@ -23949,7 +23946,7 @@
         <v>1.32</v>
       </c>
       <c r="Q494" s="62" t="s">
-        <v>994</v>
+        <v>992</v>
       </c>
     </row>
     <row r="495" spans="1:17" x14ac:dyDescent="0.55000000000000004">
@@ -23964,7 +23961,7 @@
         <v>744</v>
       </c>
       <c r="E495" s="91" t="s">
-        <v>980</v>
+        <v>979</v>
       </c>
       <c r="F495" s="89" t="s">
         <v>13</v>
@@ -24000,7 +23997,7 @@
         <v>745</v>
       </c>
       <c r="E496" s="91" t="s">
-        <v>980</v>
+        <v>979</v>
       </c>
       <c r="F496" s="89" t="s">
         <v>13</v>
@@ -24036,7 +24033,7 @@
         <v>183</v>
       </c>
       <c r="E497" s="91" t="s">
-        <v>980</v>
+        <v>979</v>
       </c>
       <c r="F497" s="89" t="s">
         <v>13</v>
@@ -24072,7 +24069,7 @@
         <v>746</v>
       </c>
       <c r="E498" s="91" t="s">
-        <v>980</v>
+        <v>979</v>
       </c>
       <c r="F498" s="89" t="s">
         <v>13</v>
@@ -24108,7 +24105,7 @@
         <v>747</v>
       </c>
       <c r="E499" s="91" t="s">
-        <v>980</v>
+        <v>979</v>
       </c>
       <c r="F499" s="89" t="s">
         <v>13</v>
@@ -24144,7 +24141,7 @@
         <v>748</v>
       </c>
       <c r="E500" s="91" t="s">
-        <v>980</v>
+        <v>979</v>
       </c>
       <c r="F500" s="89" t="s">
         <v>13</v>
@@ -24180,7 +24177,7 @@
         <v>179</v>
       </c>
       <c r="E501" s="91" t="s">
-        <v>980</v>
+        <v>979</v>
       </c>
       <c r="F501" s="89" t="s">
         <v>13</v>
@@ -24216,7 +24213,7 @@
         <v>749</v>
       </c>
       <c r="E502" s="91" t="s">
-        <v>980</v>
+        <v>979</v>
       </c>
       <c r="F502" s="89" t="s">
         <v>13</v>
@@ -24252,7 +24249,7 @@
         <v>750</v>
       </c>
       <c r="E503" s="91" t="s">
-        <v>980</v>
+        <v>979</v>
       </c>
       <c r="F503" s="89" t="s">
         <v>13</v>
@@ -24288,7 +24285,7 @@
         <v>751</v>
       </c>
       <c r="E504" s="91" t="s">
-        <v>980</v>
+        <v>979</v>
       </c>
       <c r="F504" s="89" t="s">
         <v>13</v>
@@ -24324,7 +24321,7 @@
         <v>752</v>
       </c>
       <c r="E505" s="91" t="s">
-        <v>980</v>
+        <v>979</v>
       </c>
       <c r="F505" s="89" t="s">
         <v>13</v>
@@ -24360,7 +24357,7 @@
         <v>753</v>
       </c>
       <c r="E506" s="91" t="s">
-        <v>980</v>
+        <v>979</v>
       </c>
       <c r="F506" s="89" t="s">
         <v>13</v>
@@ -24396,7 +24393,7 @@
         <v>754</v>
       </c>
       <c r="E507" s="91" t="s">
-        <v>980</v>
+        <v>979</v>
       </c>
       <c r="F507" s="89" t="s">
         <v>13</v>
@@ -24432,7 +24429,7 @@
         <v>755</v>
       </c>
       <c r="E508" s="91" t="s">
-        <v>980</v>
+        <v>979</v>
       </c>
       <c r="F508" s="89" t="s">
         <v>13</v>
@@ -24468,7 +24465,7 @@
         <v>251</v>
       </c>
       <c r="E509" s="91" t="s">
-        <v>980</v>
+        <v>979</v>
       </c>
       <c r="F509" s="89" t="s">
         <v>13</v>
@@ -24504,7 +24501,7 @@
         <v>756</v>
       </c>
       <c r="E510" s="91" t="s">
-        <v>980</v>
+        <v>979</v>
       </c>
       <c r="F510" s="89" t="s">
         <v>13</v>
@@ -24540,7 +24537,7 @@
         <v>757</v>
       </c>
       <c r="E511" s="91" t="s">
-        <v>980</v>
+        <v>979</v>
       </c>
       <c r="F511" s="89" t="s">
         <v>13</v>
@@ -24576,7 +24573,7 @@
         <v>758</v>
       </c>
       <c r="E512" s="91" t="s">
-        <v>980</v>
+        <v>979</v>
       </c>
       <c r="F512" s="89" t="s">
         <v>13</v>
@@ -24612,7 +24609,7 @@
         <v>759</v>
       </c>
       <c r="E513" s="91" t="s">
-        <v>980</v>
+        <v>979</v>
       </c>
       <c r="F513" s="89" t="s">
         <v>13</v>
@@ -24648,7 +24645,7 @@
         <v>760</v>
       </c>
       <c r="E514" s="91" t="s">
-        <v>980</v>
+        <v>979</v>
       </c>
       <c r="F514" s="89" t="s">
         <v>13</v>
@@ -24684,7 +24681,7 @@
         <v>761</v>
       </c>
       <c r="E515" s="91" t="s">
-        <v>980</v>
+        <v>979</v>
       </c>
       <c r="F515" s="89" t="s">
         <v>13</v>
@@ -24720,7 +24717,7 @@
         <v>157</v>
       </c>
       <c r="E516" s="91" t="s">
-        <v>980</v>
+        <v>979</v>
       </c>
       <c r="F516" s="89" t="s">
         <v>13</v>
@@ -24756,7 +24753,7 @@
         <v>762</v>
       </c>
       <c r="E517" s="91" t="s">
-        <v>980</v>
+        <v>979</v>
       </c>
       <c r="F517" s="89" t="s">
         <v>13</v>
@@ -24792,7 +24789,7 @@
         <v>161</v>
       </c>
       <c r="E518" s="91" t="s">
-        <v>980</v>
+        <v>979</v>
       </c>
       <c r="F518" s="89" t="s">
         <v>13</v>
@@ -24828,7 +24825,7 @@
         <v>763</v>
       </c>
       <c r="E519" s="91" t="s">
-        <v>980</v>
+        <v>979</v>
       </c>
       <c r="F519" s="89" t="s">
         <v>13</v>
@@ -24864,7 +24861,7 @@
         <v>764</v>
       </c>
       <c r="E520" s="91" t="s">
-        <v>980</v>
+        <v>979</v>
       </c>
       <c r="F520" s="89" t="s">
         <v>13</v>
@@ -24900,7 +24897,7 @@
         <v>765</v>
       </c>
       <c r="E521" s="91" t="s">
-        <v>980</v>
+        <v>979</v>
       </c>
       <c r="F521" s="89" t="s">
         <v>13</v>
@@ -24936,7 +24933,7 @@
         <v>766</v>
       </c>
       <c r="E522" s="91" t="s">
-        <v>980</v>
+        <v>979</v>
       </c>
       <c r="F522" s="89" t="s">
         <v>13</v>
@@ -24972,7 +24969,7 @@
         <v>767</v>
       </c>
       <c r="E523" s="91" t="s">
-        <v>980</v>
+        <v>979</v>
       </c>
       <c r="F523" s="89" t="s">
         <v>13</v>
@@ -25008,7 +25005,7 @@
         <v>768</v>
       </c>
       <c r="E524" s="91" t="s">
-        <v>980</v>
+        <v>979</v>
       </c>
       <c r="F524" s="89" t="s">
         <v>13</v>
@@ -25044,7 +25041,7 @@
         <v>769</v>
       </c>
       <c r="E525" s="91" t="s">
-        <v>980</v>
+        <v>979</v>
       </c>
       <c r="F525" s="89" t="s">
         <v>13</v>
@@ -25080,7 +25077,7 @@
         <v>776</v>
       </c>
       <c r="E526" s="91" t="s">
-        <v>980</v>
+        <v>979</v>
       </c>
       <c r="F526" s="88" t="s">
         <v>13</v>
@@ -25206,7 +25203,7 @@
         <v>777</v>
       </c>
       <c r="E529" s="91" t="s">
-        <v>980</v>
+        <v>979</v>
       </c>
       <c r="F529" s="88" t="s">
         <v>13</v>
@@ -25244,7 +25241,7 @@
         <v>778</v>
       </c>
       <c r="E530" s="91" t="s">
-        <v>980</v>
+        <v>979</v>
       </c>
       <c r="F530" s="88" t="s">
         <v>13</v>
@@ -25282,7 +25279,7 @@
         <v>779</v>
       </c>
       <c r="E531" s="91" t="s">
-        <v>980</v>
+        <v>979</v>
       </c>
       <c r="F531" s="88" t="s">
         <v>13</v>
@@ -25320,7 +25317,7 @@
         <v>780</v>
       </c>
       <c r="E532" s="91" t="s">
-        <v>980</v>
+        <v>979</v>
       </c>
       <c r="F532" s="88" t="s">
         <v>13</v>
@@ -25358,7 +25355,7 @@
         <v>728</v>
       </c>
       <c r="E533" s="91" t="s">
-        <v>980</v>
+        <v>979</v>
       </c>
       <c r="F533" s="88" t="s">
         <v>13</v>
@@ -25398,7 +25395,7 @@
         <v>193</v>
       </c>
       <c r="E534" s="109" t="s">
-        <v>986</v>
+        <v>985</v>
       </c>
       <c r="F534" s="109" t="s">
         <v>194</v>
@@ -25442,7 +25439,7 @@
         <v>193</v>
       </c>
       <c r="E535" s="109" t="s">
-        <v>986</v>
+        <v>985</v>
       </c>
       <c r="F535" s="109" t="s">
         <v>194</v>
@@ -25486,7 +25483,7 @@
         <v>193</v>
       </c>
       <c r="E536" s="109" t="s">
-        <v>986</v>
+        <v>985</v>
       </c>
       <c r="F536" s="109" t="s">
         <v>194</v>
@@ -25530,7 +25527,7 @@
         <v>193</v>
       </c>
       <c r="E537" s="109" t="s">
-        <v>986</v>
+        <v>985</v>
       </c>
       <c r="F537" s="109" t="s">
         <v>330</v>
@@ -25574,7 +25571,7 @@
         <v>193</v>
       </c>
       <c r="E538" s="109" t="s">
-        <v>986</v>
+        <v>985</v>
       </c>
       <c r="F538" s="109" t="s">
         <v>334</v>
@@ -25616,7 +25613,7 @@
         <v>149</v>
       </c>
       <c r="E539" s="91" t="s">
-        <v>980</v>
+        <v>979</v>
       </c>
       <c r="F539" s="89" t="s">
         <v>13</v>
@@ -25626,7 +25623,7 @@
       </c>
       <c r="H539" s="66"/>
       <c r="I539" s="86" t="s">
-        <v>995</v>
+        <v>994</v>
       </c>
       <c r="J539" s="86" t="s">
         <v>970</v>
@@ -25644,7 +25641,7 @@
         <v>189.12</v>
       </c>
       <c r="Q539" s="62" t="s">
-        <v>994</v>
+        <v>992</v>
       </c>
     </row>
     <row r="540" spans="1:17" x14ac:dyDescent="0.55000000000000004">
@@ -25659,7 +25656,7 @@
         <v>316</v>
       </c>
       <c r="E540" s="91" t="s">
-        <v>980</v>
+        <v>979</v>
       </c>
       <c r="F540" s="89" t="s">
         <v>13</v>
@@ -25669,7 +25666,7 @@
       </c>
       <c r="H540" s="66"/>
       <c r="I540" s="86" t="s">
-        <v>995</v>
+        <v>994</v>
       </c>
       <c r="J540" s="86" t="s">
         <v>970</v>
@@ -25687,7 +25684,7 @@
         <v>78.86</v>
       </c>
       <c r="Q540" s="62" t="s">
-        <v>994</v>
+        <v>992</v>
       </c>
     </row>
     <row r="541" spans="1:17" x14ac:dyDescent="0.55000000000000004">
@@ -25702,7 +25699,7 @@
         <v>781</v>
       </c>
       <c r="E541" s="91" t="s">
-        <v>980</v>
+        <v>979</v>
       </c>
       <c r="F541" s="89" t="s">
         <v>13</v>
@@ -25712,7 +25709,7 @@
       </c>
       <c r="H541" s="66"/>
       <c r="I541" s="86" t="s">
-        <v>995</v>
+        <v>994</v>
       </c>
       <c r="J541" s="86" t="s">
         <v>970</v>
@@ -25730,7 +25727,7 @@
         <v>28.69</v>
       </c>
       <c r="Q541" s="62" t="s">
-        <v>994</v>
+        <v>992</v>
       </c>
     </row>
     <row r="542" spans="1:17" x14ac:dyDescent="0.55000000000000004">
@@ -25745,7 +25742,7 @@
         <v>320</v>
       </c>
       <c r="E542" s="91" t="s">
-        <v>980</v>
+        <v>979</v>
       </c>
       <c r="F542" s="89" t="s">
         <v>13</v>
@@ -25755,7 +25752,7 @@
       </c>
       <c r="H542" s="66"/>
       <c r="I542" s="86" t="s">
-        <v>995</v>
+        <v>994</v>
       </c>
       <c r="J542" s="86" t="s">
         <v>970</v>
@@ -25773,7 +25770,7 @@
         <v>87.33</v>
       </c>
       <c r="Q542" s="62" t="s">
-        <v>994</v>
+        <v>992</v>
       </c>
     </row>
     <row r="543" spans="1:17" x14ac:dyDescent="0.55000000000000004">
@@ -25788,7 +25785,7 @@
         <v>151</v>
       </c>
       <c r="E543" s="91" t="s">
-        <v>980</v>
+        <v>979</v>
       </c>
       <c r="F543" s="89" t="s">
         <v>13</v>
@@ -25798,7 +25795,7 @@
       </c>
       <c r="H543" s="66"/>
       <c r="I543" s="86" t="s">
-        <v>995</v>
+        <v>994</v>
       </c>
       <c r="J543" s="86" t="s">
         <v>970</v>
@@ -25816,7 +25813,7 @@
         <v>38.200000000000003</v>
       </c>
       <c r="Q543" s="62" t="s">
-        <v>994</v>
+        <v>992</v>
       </c>
     </row>
     <row r="544" spans="1:17" x14ac:dyDescent="0.55000000000000004">
@@ -25831,7 +25828,7 @@
         <v>782</v>
       </c>
       <c r="E544" s="91" t="s">
-        <v>980</v>
+        <v>979</v>
       </c>
       <c r="F544" s="89" t="s">
         <v>13</v>
@@ -25841,7 +25838,7 @@
       </c>
       <c r="H544" s="66"/>
       <c r="I544" s="86" t="s">
-        <v>995</v>
+        <v>994</v>
       </c>
       <c r="J544" s="86" t="s">
         <v>970</v>
@@ -25859,7 +25856,7 @@
         <v>64.98</v>
       </c>
       <c r="Q544" s="62" t="s">
-        <v>994</v>
+        <v>992</v>
       </c>
     </row>
     <row r="545" spans="1:17" x14ac:dyDescent="0.55000000000000004">
@@ -25874,7 +25871,7 @@
         <v>187</v>
       </c>
       <c r="E545" s="91" t="s">
-        <v>980</v>
+        <v>979</v>
       </c>
       <c r="F545" s="89" t="s">
         <v>13</v>
@@ -25884,7 +25881,7 @@
       </c>
       <c r="H545" s="66"/>
       <c r="I545" s="86" t="s">
-        <v>995</v>
+        <v>994</v>
       </c>
       <c r="J545" s="86" t="s">
         <v>970</v>
@@ -25902,7 +25899,7 @@
         <v>134.30000000000001</v>
       </c>
       <c r="Q545" s="62" t="s">
-        <v>994</v>
+        <v>992</v>
       </c>
     </row>
     <row r="546" spans="1:17" x14ac:dyDescent="0.55000000000000004">
@@ -25917,7 +25914,7 @@
         <v>185</v>
       </c>
       <c r="E546" s="91" t="s">
-        <v>980</v>
+        <v>979</v>
       </c>
       <c r="F546" s="89" t="s">
         <v>13</v>
@@ -25927,7 +25924,7 @@
       </c>
       <c r="H546" s="66"/>
       <c r="I546" s="86" t="s">
-        <v>995</v>
+        <v>994</v>
       </c>
       <c r="J546" s="86" t="s">
         <v>970</v>
@@ -25945,7 +25942,7 @@
         <v>43.13</v>
       </c>
       <c r="Q546" s="62" t="s">
-        <v>994</v>
+        <v>992</v>
       </c>
     </row>
     <row r="547" spans="1:17" x14ac:dyDescent="0.55000000000000004">
@@ -25960,7 +25957,7 @@
         <v>783</v>
       </c>
       <c r="E547" s="91" t="s">
-        <v>980</v>
+        <v>979</v>
       </c>
       <c r="F547" s="89" t="s">
         <v>13</v>
@@ -25970,7 +25967,7 @@
       </c>
       <c r="H547" s="66"/>
       <c r="I547" s="86" t="s">
-        <v>995</v>
+        <v>994</v>
       </c>
       <c r="J547" s="86" t="s">
         <v>970</v>
@@ -25988,7 +25985,7 @@
         <v>80.31</v>
       </c>
       <c r="Q547" s="62" t="s">
-        <v>994</v>
+        <v>992</v>
       </c>
     </row>
     <row r="548" spans="1:17" x14ac:dyDescent="0.55000000000000004">
@@ -26003,7 +26000,7 @@
         <v>784</v>
       </c>
       <c r="E548" s="91" t="s">
-        <v>980</v>
+        <v>979</v>
       </c>
       <c r="F548" s="89" t="s">
         <v>13</v>
@@ -26013,7 +26010,7 @@
       </c>
       <c r="H548" s="66"/>
       <c r="I548" s="86" t="s">
-        <v>995</v>
+        <v>994</v>
       </c>
       <c r="J548" s="86" t="s">
         <v>970</v>
@@ -26031,7 +26028,7 @@
         <v>34.96</v>
       </c>
       <c r="Q548" s="62" t="s">
-        <v>994</v>
+        <v>992</v>
       </c>
     </row>
     <row r="549" spans="1:17" x14ac:dyDescent="0.55000000000000004">
@@ -26046,7 +26043,7 @@
         <v>785</v>
       </c>
       <c r="E549" s="91" t="s">
-        <v>980</v>
+        <v>979</v>
       </c>
       <c r="F549" s="89" t="s">
         <v>13</v>
@@ -26056,7 +26053,7 @@
       </c>
       <c r="H549" s="66"/>
       <c r="I549" s="86" t="s">
-        <v>995</v>
+        <v>994</v>
       </c>
       <c r="J549" s="86" t="s">
         <v>970</v>
@@ -26074,7 +26071,7 @@
         <v>59.61</v>
       </c>
       <c r="Q549" s="62" t="s">
-        <v>994</v>
+        <v>992</v>
       </c>
     </row>
     <row r="550" spans="1:17" x14ac:dyDescent="0.55000000000000004">
@@ -26089,7 +26086,7 @@
         <v>786</v>
       </c>
       <c r="E550" s="91" t="s">
-        <v>980</v>
+        <v>979</v>
       </c>
       <c r="F550" s="89" t="s">
         <v>13</v>
@@ -26099,7 +26096,7 @@
       </c>
       <c r="H550" s="66"/>
       <c r="I550" s="86" t="s">
-        <v>995</v>
+        <v>994</v>
       </c>
       <c r="J550" s="86" t="s">
         <v>970</v>
@@ -26117,7 +26114,7 @@
         <v>42.64</v>
       </c>
       <c r="Q550" s="62" t="s">
-        <v>994</v>
+        <v>992</v>
       </c>
     </row>
     <row r="551" spans="1:17" x14ac:dyDescent="0.55000000000000004">
@@ -26132,7 +26129,7 @@
         <v>787</v>
       </c>
       <c r="E551" s="91" t="s">
-        <v>980</v>
+        <v>979</v>
       </c>
       <c r="F551" s="89" t="s">
         <v>13</v>
@@ -26142,7 +26139,7 @@
       </c>
       <c r="H551" s="66"/>
       <c r="I551" s="86" t="s">
-        <v>995</v>
+        <v>994</v>
       </c>
       <c r="J551" s="86" t="s">
         <v>970</v>
@@ -26160,7 +26157,7 @@
         <v>11.48</v>
       </c>
       <c r="Q551" s="62" t="s">
-        <v>994</v>
+        <v>992</v>
       </c>
     </row>
     <row r="552" spans="1:17" x14ac:dyDescent="0.55000000000000004">
@@ -26175,7 +26172,7 @@
         <v>788</v>
       </c>
       <c r="E552" s="91" t="s">
-        <v>980</v>
+        <v>979</v>
       </c>
       <c r="F552" s="89" t="s">
         <v>13</v>
@@ -26185,7 +26182,7 @@
       </c>
       <c r="H552" s="66"/>
       <c r="I552" s="86" t="s">
-        <v>995</v>
+        <v>994</v>
       </c>
       <c r="J552" s="86" t="s">
         <v>970</v>
@@ -26203,7 +26200,7 @@
         <v>11.3</v>
       </c>
       <c r="Q552" s="62" t="s">
-        <v>994</v>
+        <v>992</v>
       </c>
     </row>
     <row r="553" spans="1:17" x14ac:dyDescent="0.55000000000000004">
@@ -26218,7 +26215,7 @@
         <v>789</v>
       </c>
       <c r="E553" s="91" t="s">
-        <v>980</v>
+        <v>979</v>
       </c>
       <c r="F553" s="89" t="s">
         <v>13</v>
@@ -26228,7 +26225,7 @@
       </c>
       <c r="H553" s="66"/>
       <c r="I553" s="86" t="s">
-        <v>995</v>
+        <v>994</v>
       </c>
       <c r="J553" s="86" t="s">
         <v>970</v>
@@ -26246,7 +26243,7 @@
         <v>25.09</v>
       </c>
       <c r="Q553" s="62" t="s">
-        <v>994</v>
+        <v>992</v>
       </c>
     </row>
     <row r="554" spans="1:17" x14ac:dyDescent="0.55000000000000004">
@@ -26261,7 +26258,7 @@
         <v>311</v>
       </c>
       <c r="E554" s="91" t="s">
-        <v>980</v>
+        <v>979</v>
       </c>
       <c r="F554" s="89" t="s">
         <v>13</v>
@@ -26271,7 +26268,7 @@
       </c>
       <c r="H554" s="66"/>
       <c r="I554" s="86" t="s">
-        <v>995</v>
+        <v>994</v>
       </c>
       <c r="J554" s="86" t="s">
         <v>970</v>
@@ -26289,7 +26286,7 @@
         <v>12.72</v>
       </c>
       <c r="Q554" s="62" t="s">
-        <v>994</v>
+        <v>992</v>
       </c>
     </row>
     <row r="555" spans="1:17" x14ac:dyDescent="0.55000000000000004">
@@ -26304,7 +26301,7 @@
         <v>790</v>
       </c>
       <c r="E555" s="91" t="s">
-        <v>980</v>
+        <v>979</v>
       </c>
       <c r="F555" s="89" t="s">
         <v>13</v>
@@ -26314,7 +26311,7 @@
       </c>
       <c r="H555" s="66"/>
       <c r="I555" s="86" t="s">
-        <v>995</v>
+        <v>994</v>
       </c>
       <c r="J555" s="86" t="s">
         <v>970</v>
@@ -26332,7 +26329,7 @@
         <v>12.72</v>
       </c>
       <c r="Q555" s="62" t="s">
-        <v>994</v>
+        <v>992</v>
       </c>
     </row>
     <row r="556" spans="1:17" x14ac:dyDescent="0.55000000000000004">
@@ -26347,7 +26344,7 @@
         <v>791</v>
       </c>
       <c r="E556" s="91" t="s">
-        <v>980</v>
+        <v>979</v>
       </c>
       <c r="F556" s="89" t="s">
         <v>13</v>
@@ -26357,7 +26354,7 @@
       </c>
       <c r="H556" s="66"/>
       <c r="I556" s="86" t="s">
-        <v>995</v>
+        <v>994</v>
       </c>
       <c r="J556" s="86" t="s">
         <v>970</v>
@@ -26375,7 +26372,7 @@
         <v>12.72</v>
       </c>
       <c r="Q556" s="62" t="s">
-        <v>994</v>
+        <v>992</v>
       </c>
     </row>
     <row r="557" spans="1:17" x14ac:dyDescent="0.55000000000000004">
@@ -26390,7 +26387,7 @@
         <v>792</v>
       </c>
       <c r="E557" s="91" t="s">
-        <v>980</v>
+        <v>979</v>
       </c>
       <c r="F557" s="89" t="s">
         <v>13</v>
@@ -26400,7 +26397,7 @@
       </c>
       <c r="H557" s="66"/>
       <c r="I557" s="86" t="s">
-        <v>995</v>
+        <v>994</v>
       </c>
       <c r="J557" s="86" t="s">
         <v>970</v>
@@ -26418,7 +26415,7 @@
         <v>12.72</v>
       </c>
       <c r="Q557" s="62" t="s">
-        <v>994</v>
+        <v>992</v>
       </c>
     </row>
     <row r="558" spans="1:17" x14ac:dyDescent="0.55000000000000004">
@@ -26433,7 +26430,7 @@
         <v>793</v>
       </c>
       <c r="E558" s="91" t="s">
-        <v>980</v>
+        <v>979</v>
       </c>
       <c r="F558" s="89" t="s">
         <v>13</v>
@@ -26443,7 +26440,7 @@
       </c>
       <c r="H558" s="66"/>
       <c r="I558" s="86" t="s">
-        <v>995</v>
+        <v>994</v>
       </c>
       <c r="J558" s="86" t="s">
         <v>970</v>
@@ -26461,7 +26458,7 @@
         <v>258.08</v>
       </c>
       <c r="Q558" s="62" t="s">
-        <v>994</v>
+        <v>992</v>
       </c>
     </row>
     <row r="559" spans="1:17" x14ac:dyDescent="0.55000000000000004">
@@ -26476,7 +26473,7 @@
         <v>260</v>
       </c>
       <c r="E559" s="91" t="s">
-        <v>980</v>
+        <v>979</v>
       </c>
       <c r="F559" s="89" t="s">
         <v>13</v>
@@ -26514,7 +26511,7 @@
         <v>735</v>
       </c>
       <c r="E560" s="91" t="s">
-        <v>980</v>
+        <v>979</v>
       </c>
       <c r="F560" s="89" t="s">
         <v>13</v>
@@ -26524,7 +26521,7 @@
       </c>
       <c r="H560" s="66"/>
       <c r="I560" s="86" t="s">
-        <v>974</v>
+        <v>995</v>
       </c>
       <c r="J560" s="86" t="s">
         <v>970</v>
@@ -26552,7 +26549,7 @@
         <v>736</v>
       </c>
       <c r="E561" s="91" t="s">
-        <v>980</v>
+        <v>979</v>
       </c>
       <c r="F561" s="89" t="s">
         <v>13</v>
@@ -26562,7 +26559,7 @@
       </c>
       <c r="H561" s="66"/>
       <c r="I561" s="86" t="s">
-        <v>974</v>
+        <v>995</v>
       </c>
       <c r="J561" s="86" t="s">
         <v>970</v>
@@ -26590,7 +26587,7 @@
         <v>795</v>
       </c>
       <c r="E562" s="91" t="s">
-        <v>980</v>
+        <v>979</v>
       </c>
       <c r="F562" s="89" t="s">
         <v>13</v>
@@ -26626,7 +26623,7 @@
         <v>796</v>
       </c>
       <c r="E563" s="91" t="s">
-        <v>980</v>
+        <v>979</v>
       </c>
       <c r="F563" s="89" t="s">
         <v>13</v>
@@ -26662,7 +26659,7 @@
         <v>797</v>
       </c>
       <c r="E564" s="91" t="s">
-        <v>980</v>
+        <v>979</v>
       </c>
       <c r="F564" s="89" t="s">
         <v>13</v>
@@ -26698,7 +26695,7 @@
         <v>798</v>
       </c>
       <c r="E565" s="91" t="s">
-        <v>980</v>
+        <v>979</v>
       </c>
       <c r="F565" s="89" t="s">
         <v>13</v>
@@ -26734,7 +26731,7 @@
         <v>799</v>
       </c>
       <c r="E566" s="91" t="s">
-        <v>980</v>
+        <v>979</v>
       </c>
       <c r="F566" s="89" t="s">
         <v>13</v>
@@ -26770,7 +26767,7 @@
         <v>800</v>
       </c>
       <c r="E567" s="91" t="s">
-        <v>980</v>
+        <v>979</v>
       </c>
       <c r="F567" s="89" t="s">
         <v>13</v>
@@ -26806,7 +26803,7 @@
         <v>801</v>
       </c>
       <c r="E568" s="91" t="s">
-        <v>980</v>
+        <v>979</v>
       </c>
       <c r="F568" s="89" t="s">
         <v>13</v>
@@ -26842,7 +26839,7 @@
         <v>802</v>
       </c>
       <c r="E569" s="91" t="s">
-        <v>980</v>
+        <v>979</v>
       </c>
       <c r="F569" s="89" t="s">
         <v>13</v>
@@ -26878,7 +26875,7 @@
         <v>803</v>
       </c>
       <c r="E570" s="91" t="s">
-        <v>980</v>
+        <v>979</v>
       </c>
       <c r="F570" s="89" t="s">
         <v>13</v>
@@ -26914,7 +26911,7 @@
         <v>804</v>
       </c>
       <c r="E571" s="91" t="s">
-        <v>980</v>
+        <v>979</v>
       </c>
       <c r="F571" s="89" t="s">
         <v>13</v>
@@ -26950,7 +26947,7 @@
         <v>805</v>
       </c>
       <c r="E572" s="91" t="s">
-        <v>980</v>
+        <v>979</v>
       </c>
       <c r="F572" s="89" t="s">
         <v>13</v>
@@ -26986,7 +26983,7 @@
         <v>806</v>
       </c>
       <c r="E573" s="91" t="s">
-        <v>980</v>
+        <v>979</v>
       </c>
       <c r="F573" s="89" t="s">
         <v>13</v>
@@ -27022,7 +27019,7 @@
         <v>807</v>
       </c>
       <c r="E574" s="91" t="s">
-        <v>980</v>
+        <v>979</v>
       </c>
       <c r="F574" s="89" t="s">
         <v>13</v>
@@ -27058,7 +27055,7 @@
         <v>808</v>
       </c>
       <c r="E575" s="91" t="s">
-        <v>980</v>
+        <v>979</v>
       </c>
       <c r="F575" s="89" t="s">
         <v>13</v>
@@ -27094,7 +27091,7 @@
         <v>258</v>
       </c>
       <c r="E576" s="91" t="s">
-        <v>980</v>
+        <v>979</v>
       </c>
       <c r="F576" s="89" t="s">
         <v>13</v>
@@ -27130,7 +27127,7 @@
         <v>809</v>
       </c>
       <c r="E577" s="91" t="s">
-        <v>980</v>
+        <v>979</v>
       </c>
       <c r="F577" s="89" t="s">
         <v>13</v>
@@ -27166,7 +27163,7 @@
         <v>256</v>
       </c>
       <c r="E578" s="91" t="s">
-        <v>980</v>
+        <v>979</v>
       </c>
       <c r="F578" s="89" t="s">
         <v>13</v>
@@ -27202,7 +27199,7 @@
         <v>810</v>
       </c>
       <c r="E579" s="91" t="s">
-        <v>980</v>
+        <v>979</v>
       </c>
       <c r="F579" s="89" t="s">
         <v>13</v>
@@ -27238,7 +27235,7 @@
         <v>255</v>
       </c>
       <c r="E580" s="91" t="s">
-        <v>980</v>
+        <v>979</v>
       </c>
       <c r="F580" s="89" t="s">
         <v>13</v>
@@ -27274,7 +27271,7 @@
         <v>811</v>
       </c>
       <c r="E581" s="91" t="s">
-        <v>980</v>
+        <v>979</v>
       </c>
       <c r="F581" s="89" t="s">
         <v>13</v>
@@ -27310,7 +27307,7 @@
         <v>812</v>
       </c>
       <c r="E582" s="91" t="s">
-        <v>980</v>
+        <v>979</v>
       </c>
       <c r="F582" s="89" t="s">
         <v>13</v>
@@ -27346,7 +27343,7 @@
         <v>813</v>
       </c>
       <c r="E583" s="91" t="s">
-        <v>980</v>
+        <v>979</v>
       </c>
       <c r="F583" s="89" t="s">
         <v>13</v>
@@ -27382,7 +27379,7 @@
         <v>170</v>
       </c>
       <c r="E584" s="91" t="s">
-        <v>980</v>
+        <v>979</v>
       </c>
       <c r="F584" s="89" t="s">
         <v>13</v>
@@ -27418,7 +27415,7 @@
         <v>814</v>
       </c>
       <c r="E585" s="91" t="s">
-        <v>980</v>
+        <v>979</v>
       </c>
       <c r="F585" s="89" t="s">
         <v>13</v>
@@ -27454,7 +27451,7 @@
         <v>815</v>
       </c>
       <c r="E586" s="91" t="s">
-        <v>980</v>
+        <v>979</v>
       </c>
       <c r="F586" s="89" t="s">
         <v>13</v>
@@ -27490,7 +27487,7 @@
         <v>816</v>
       </c>
       <c r="E587" s="91" t="s">
-        <v>980</v>
+        <v>979</v>
       </c>
       <c r="F587" s="89" t="s">
         <v>13</v>
@@ -27526,7 +27523,7 @@
         <v>817</v>
       </c>
       <c r="E588" s="91" t="s">
-        <v>980</v>
+        <v>979</v>
       </c>
       <c r="F588" s="89" t="s">
         <v>13</v>
@@ -27562,7 +27559,7 @@
         <v>164</v>
       </c>
       <c r="E589" s="91" t="s">
-        <v>980</v>
+        <v>979</v>
       </c>
       <c r="F589" s="89" t="s">
         <v>13</v>
@@ -27598,7 +27595,7 @@
         <v>818</v>
       </c>
       <c r="E590" s="91" t="s">
-        <v>980</v>
+        <v>979</v>
       </c>
       <c r="F590" s="89" t="s">
         <v>13</v>
@@ -27634,7 +27631,7 @@
         <v>175</v>
       </c>
       <c r="E591" s="91" t="s">
-        <v>980</v>
+        <v>979</v>
       </c>
       <c r="F591" s="89" t="s">
         <v>13</v>
@@ -27670,7 +27667,7 @@
         <v>819</v>
       </c>
       <c r="E592" s="91" t="s">
-        <v>980</v>
+        <v>979</v>
       </c>
       <c r="F592" s="89" t="s">
         <v>13</v>
@@ -27706,7 +27703,7 @@
         <v>820</v>
       </c>
       <c r="E593" s="91" t="s">
-        <v>980</v>
+        <v>979</v>
       </c>
       <c r="F593" s="89" t="s">
         <v>13</v>
@@ -27742,7 +27739,7 @@
         <v>821</v>
       </c>
       <c r="E594" s="91" t="s">
-        <v>980</v>
+        <v>979</v>
       </c>
       <c r="F594" s="89" t="s">
         <v>13</v>
@@ -27778,7 +27775,7 @@
         <v>822</v>
       </c>
       <c r="E595" s="91" t="s">
-        <v>980</v>
+        <v>979</v>
       </c>
       <c r="F595" s="89" t="s">
         <v>13</v>
@@ -27814,7 +27811,7 @@
         <v>823</v>
       </c>
       <c r="E596" s="91" t="s">
-        <v>980</v>
+        <v>979</v>
       </c>
       <c r="F596" s="89" t="s">
         <v>13</v>
@@ -27850,7 +27847,7 @@
         <v>297</v>
       </c>
       <c r="E597" s="91" t="s">
-        <v>980</v>
+        <v>979</v>
       </c>
       <c r="F597" s="89" t="s">
         <v>13</v>
@@ -27860,7 +27857,7 @@
       </c>
       <c r="H597" s="66"/>
       <c r="I597" s="86" t="s">
-        <v>995</v>
+        <v>994</v>
       </c>
       <c r="J597" s="86" t="s">
         <v>970</v>
@@ -27878,7 +27875,7 @@
         <v>7.65</v>
       </c>
       <c r="Q597" s="62" t="s">
-        <v>994</v>
+        <v>992</v>
       </c>
     </row>
     <row r="598" spans="1:17" x14ac:dyDescent="0.55000000000000004">
@@ -27893,7 +27890,7 @@
         <v>290</v>
       </c>
       <c r="E598" s="91" t="s">
-        <v>980</v>
+        <v>979</v>
       </c>
       <c r="F598" s="89" t="s">
         <v>13</v>
@@ -27903,7 +27900,7 @@
       </c>
       <c r="H598" s="66"/>
       <c r="I598" s="86" t="s">
-        <v>995</v>
+        <v>994</v>
       </c>
       <c r="J598" s="86" t="s">
         <v>970</v>
@@ -27921,7 +27918,7 @@
         <v>13.05</v>
       </c>
       <c r="Q598" s="62" t="s">
-        <v>994</v>
+        <v>992</v>
       </c>
     </row>
     <row r="599" spans="1:17" x14ac:dyDescent="0.55000000000000004">
@@ -27936,7 +27933,7 @@
         <v>293</v>
       </c>
       <c r="E599" s="91" t="s">
-        <v>980</v>
+        <v>979</v>
       </c>
       <c r="F599" s="89" t="s">
         <v>13</v>
@@ -27946,7 +27943,7 @@
       </c>
       <c r="H599" s="66"/>
       <c r="I599" s="86" t="s">
-        <v>995</v>
+        <v>994</v>
       </c>
       <c r="J599" s="86" t="s">
         <v>970</v>
@@ -27964,7 +27961,7 @@
         <v>66.989999999999995</v>
       </c>
       <c r="Q599" s="62" t="s">
-        <v>994</v>
+        <v>992</v>
       </c>
     </row>
     <row r="600" spans="1:17" x14ac:dyDescent="0.55000000000000004">
@@ -27979,7 +27976,7 @@
         <v>824</v>
       </c>
       <c r="E600" s="91" t="s">
-        <v>980</v>
+        <v>979</v>
       </c>
       <c r="F600" s="89" t="s">
         <v>13</v>
@@ -27989,7 +27986,7 @@
       </c>
       <c r="H600" s="66"/>
       <c r="I600" s="86" t="s">
-        <v>995</v>
+        <v>994</v>
       </c>
       <c r="J600" s="86" t="s">
         <v>970</v>
@@ -28007,7 +28004,7 @@
         <v>7.91</v>
       </c>
       <c r="Q600" s="62" t="s">
-        <v>994</v>
+        <v>992</v>
       </c>
     </row>
     <row r="601" spans="1:17" x14ac:dyDescent="0.55000000000000004">
@@ -28022,7 +28019,7 @@
         <v>825</v>
       </c>
       <c r="E601" s="91" t="s">
-        <v>980</v>
+        <v>979</v>
       </c>
       <c r="F601" s="89" t="s">
         <v>13</v>
@@ -28032,7 +28029,7 @@
       </c>
       <c r="H601" s="66"/>
       <c r="I601" s="86" t="s">
-        <v>995</v>
+        <v>994</v>
       </c>
       <c r="J601" s="86" t="s">
         <v>970</v>
@@ -28050,7 +28047,7 @@
         <v>7.65</v>
       </c>
       <c r="Q601" s="62" t="s">
-        <v>994</v>
+        <v>992</v>
       </c>
     </row>
     <row r="602" spans="1:17" x14ac:dyDescent="0.55000000000000004">
@@ -28065,7 +28062,7 @@
         <v>826</v>
       </c>
       <c r="E602" s="91" t="s">
-        <v>980</v>
+        <v>979</v>
       </c>
       <c r="F602" s="89" t="s">
         <v>13</v>
@@ -28075,7 +28072,7 @@
       </c>
       <c r="H602" s="66"/>
       <c r="I602" s="86" t="s">
-        <v>995</v>
+        <v>994</v>
       </c>
       <c r="J602" s="86" t="s">
         <v>970</v>
@@ -28093,7 +28090,7 @@
         <v>7.91</v>
       </c>
       <c r="Q602" s="62" t="s">
-        <v>994</v>
+        <v>992</v>
       </c>
     </row>
     <row r="603" spans="1:17" x14ac:dyDescent="0.55000000000000004">
@@ -28108,7 +28105,7 @@
         <v>147</v>
       </c>
       <c r="E603" s="91" t="s">
-        <v>980</v>
+        <v>979</v>
       </c>
       <c r="F603" s="89" t="s">
         <v>13</v>
@@ -28118,7 +28115,7 @@
       </c>
       <c r="H603" s="66"/>
       <c r="I603" s="86" t="s">
-        <v>995</v>
+        <v>994</v>
       </c>
       <c r="J603" s="86" t="s">
         <v>970</v>
@@ -28136,7 +28133,7 @@
         <v>37.909999999999997</v>
       </c>
       <c r="Q603" s="62" t="s">
-        <v>994</v>
+        <v>992</v>
       </c>
     </row>
     <row r="604" spans="1:17" x14ac:dyDescent="0.55000000000000004">
@@ -28151,7 +28148,7 @@
         <v>827</v>
       </c>
       <c r="E604" s="91" t="s">
-        <v>980</v>
+        <v>979</v>
       </c>
       <c r="F604" s="89" t="s">
         <v>13</v>
@@ -28161,7 +28158,7 @@
       </c>
       <c r="H604" s="66"/>
       <c r="I604" s="86" t="s">
-        <v>995</v>
+        <v>994</v>
       </c>
       <c r="J604" s="86" t="s">
         <v>970</v>
@@ -28179,7 +28176,7 @@
         <v>7.2</v>
       </c>
       <c r="Q604" s="62" t="s">
-        <v>994</v>
+        <v>992</v>
       </c>
     </row>
     <row r="605" spans="1:17" x14ac:dyDescent="0.55000000000000004">
@@ -28194,7 +28191,7 @@
         <v>828</v>
       </c>
       <c r="E605" s="91" t="s">
-        <v>980</v>
+        <v>979</v>
       </c>
       <c r="F605" s="89" t="s">
         <v>13</v>
@@ -28230,7 +28227,7 @@
         <v>829</v>
       </c>
       <c r="E606" s="91" t="s">
-        <v>980</v>
+        <v>979</v>
       </c>
       <c r="F606" s="89" t="s">
         <v>13</v>
@@ -28266,7 +28263,7 @@
         <v>830</v>
       </c>
       <c r="E607" s="91" t="s">
-        <v>980</v>
+        <v>979</v>
       </c>
       <c r="F607" s="89" t="s">
         <v>13</v>
@@ -28302,7 +28299,7 @@
         <v>831</v>
       </c>
       <c r="E608" s="91" t="s">
-        <v>980</v>
+        <v>979</v>
       </c>
       <c r="F608" s="89" t="s">
         <v>13</v>
@@ -28338,7 +28335,7 @@
         <v>832</v>
       </c>
       <c r="E609" s="91" t="s">
-        <v>980</v>
+        <v>979</v>
       </c>
       <c r="F609" s="89" t="s">
         <v>13</v>
@@ -28374,7 +28371,7 @@
         <v>833</v>
       </c>
       <c r="E610" s="91" t="s">
-        <v>980</v>
+        <v>979</v>
       </c>
       <c r="F610" s="89" t="s">
         <v>13</v>
@@ -28410,7 +28407,7 @@
         <v>834</v>
       </c>
       <c r="E611" s="91" t="s">
-        <v>980</v>
+        <v>979</v>
       </c>
       <c r="F611" s="89" t="s">
         <v>13</v>
@@ -28446,7 +28443,7 @@
         <v>835</v>
       </c>
       <c r="E612" s="91" t="s">
-        <v>980</v>
+        <v>979</v>
       </c>
       <c r="F612" s="89" t="s">
         <v>13</v>
@@ -28482,7 +28479,7 @@
         <v>836</v>
       </c>
       <c r="E613" s="91" t="s">
-        <v>980</v>
+        <v>979</v>
       </c>
       <c r="F613" s="89" t="s">
         <v>13</v>
@@ -28518,7 +28515,7 @@
         <v>837</v>
       </c>
       <c r="E614" s="91" t="s">
-        <v>980</v>
+        <v>979</v>
       </c>
       <c r="F614" s="89" t="s">
         <v>13</v>
@@ -28554,7 +28551,7 @@
         <v>838</v>
       </c>
       <c r="E615" s="91" t="s">
-        <v>980</v>
+        <v>979</v>
       </c>
       <c r="F615" s="89" t="s">
         <v>13</v>
@@ -28590,7 +28587,7 @@
         <v>839</v>
       </c>
       <c r="E616" s="91" t="s">
-        <v>980</v>
+        <v>979</v>
       </c>
       <c r="F616" s="89" t="s">
         <v>13</v>
@@ -28626,7 +28623,7 @@
         <v>840</v>
       </c>
       <c r="E617" s="91" t="s">
-        <v>980</v>
+        <v>979</v>
       </c>
       <c r="F617" s="89" t="s">
         <v>13</v>
@@ -28662,7 +28659,7 @@
         <v>210</v>
       </c>
       <c r="E618" s="91" t="s">
-        <v>980</v>
+        <v>979</v>
       </c>
       <c r="F618" s="89" t="s">
         <v>13</v>
@@ -28698,7 +28695,7 @@
         <v>841</v>
       </c>
       <c r="E619" s="91" t="s">
-        <v>980</v>
+        <v>979</v>
       </c>
       <c r="F619" s="89" t="s">
         <v>13</v>
@@ -28734,7 +28731,7 @@
         <v>842</v>
       </c>
       <c r="E620" s="91" t="s">
-        <v>980</v>
+        <v>979</v>
       </c>
       <c r="F620" s="89" t="s">
         <v>13</v>
@@ -28770,7 +28767,7 @@
         <v>843</v>
       </c>
       <c r="E621" s="91" t="s">
-        <v>980</v>
+        <v>979</v>
       </c>
       <c r="F621" s="89" t="s">
         <v>13</v>
@@ -28806,7 +28803,7 @@
         <v>844</v>
       </c>
       <c r="E622" s="91" t="s">
-        <v>980</v>
+        <v>979</v>
       </c>
       <c r="F622" s="89" t="s">
         <v>13</v>
@@ -28842,7 +28839,7 @@
         <v>845</v>
       </c>
       <c r="E623" s="91" t="s">
-        <v>980</v>
+        <v>979</v>
       </c>
       <c r="F623" s="89" t="s">
         <v>13</v>
@@ -28878,7 +28875,7 @@
         <v>846</v>
       </c>
       <c r="E624" s="91" t="s">
-        <v>980</v>
+        <v>979</v>
       </c>
       <c r="F624" s="89" t="s">
         <v>13</v>
@@ -28914,7 +28911,7 @@
         <v>847</v>
       </c>
       <c r="E625" s="91" t="s">
-        <v>980</v>
+        <v>979</v>
       </c>
       <c r="F625" s="89" t="s">
         <v>13</v>
@@ -28950,7 +28947,7 @@
         <v>848</v>
       </c>
       <c r="E626" s="91" t="s">
-        <v>980</v>
+        <v>979</v>
       </c>
       <c r="F626" s="89" t="s">
         <v>13</v>
@@ -28986,7 +28983,7 @@
         <v>849</v>
       </c>
       <c r="E627" s="91" t="s">
-        <v>980</v>
+        <v>979</v>
       </c>
       <c r="F627" s="89" t="s">
         <v>13</v>
@@ -29022,7 +29019,7 @@
         <v>850</v>
       </c>
       <c r="E628" s="91" t="s">
-        <v>980</v>
+        <v>979</v>
       </c>
       <c r="F628" s="89" t="s">
         <v>13</v>
@@ -29058,7 +29055,7 @@
         <v>851</v>
       </c>
       <c r="E629" s="91" t="s">
-        <v>980</v>
+        <v>979</v>
       </c>
       <c r="F629" s="89" t="s">
         <v>13</v>
@@ -29094,7 +29091,7 @@
         <v>852</v>
       </c>
       <c r="E630" s="91" t="s">
-        <v>980</v>
+        <v>979</v>
       </c>
       <c r="F630" s="89" t="s">
         <v>13</v>
@@ -29130,7 +29127,7 @@
         <v>853</v>
       </c>
       <c r="E631" s="91" t="s">
-        <v>980</v>
+        <v>979</v>
       </c>
       <c r="F631" s="89" t="s">
         <v>13</v>
@@ -29166,7 +29163,7 @@
         <v>854</v>
       </c>
       <c r="E632" s="91" t="s">
-        <v>980</v>
+        <v>979</v>
       </c>
       <c r="F632" s="89" t="s">
         <v>13</v>
@@ -29202,7 +29199,7 @@
         <v>855</v>
       </c>
       <c r="E633" s="91" t="s">
-        <v>980</v>
+        <v>979</v>
       </c>
       <c r="F633" s="89" t="s">
         <v>13</v>
@@ -29238,7 +29235,7 @@
         <v>856</v>
       </c>
       <c r="E634" s="91" t="s">
-        <v>980</v>
+        <v>979</v>
       </c>
       <c r="F634" s="89" t="s">
         <v>13</v>
@@ -29274,7 +29271,7 @@
         <v>857</v>
       </c>
       <c r="E635" s="91" t="s">
-        <v>980</v>
+        <v>979</v>
       </c>
       <c r="F635" s="89" t="s">
         <v>13</v>
@@ -29310,7 +29307,7 @@
         <v>858</v>
       </c>
       <c r="E636" s="91" t="s">
-        <v>980</v>
+        <v>979</v>
       </c>
       <c r="F636" s="89" t="s">
         <v>13</v>
@@ -29346,7 +29343,7 @@
         <v>247</v>
       </c>
       <c r="E637" s="91" t="s">
-        <v>980</v>
+        <v>979</v>
       </c>
       <c r="F637" s="89" t="s">
         <v>13</v>
@@ -29382,7 +29379,7 @@
         <v>859</v>
       </c>
       <c r="E638" s="91" t="s">
-        <v>980</v>
+        <v>979</v>
       </c>
       <c r="F638" s="89" t="s">
         <v>13</v>
@@ -29418,7 +29415,7 @@
         <v>142</v>
       </c>
       <c r="E639" s="91" t="s">
-        <v>980</v>
+        <v>979</v>
       </c>
       <c r="F639" s="89" t="s">
         <v>13</v>
@@ -29428,7 +29425,7 @@
       </c>
       <c r="H639" s="66"/>
       <c r="I639" s="86" t="s">
-        <v>995</v>
+        <v>994</v>
       </c>
       <c r="J639" s="86" t="s">
         <v>970</v>
@@ -29446,7 +29443,7 @@
         <v>42.8</v>
       </c>
       <c r="Q639" s="62" t="s">
-        <v>994</v>
+        <v>992</v>
       </c>
     </row>
     <row r="640" spans="1:17" x14ac:dyDescent="0.55000000000000004">
@@ -29461,7 +29458,7 @@
         <v>191</v>
       </c>
       <c r="E640" s="91" t="s">
-        <v>980</v>
+        <v>979</v>
       </c>
       <c r="F640" s="89" t="s">
         <v>13</v>
@@ -29471,7 +29468,7 @@
       </c>
       <c r="H640" s="66"/>
       <c r="I640" s="86" t="s">
-        <v>995</v>
+        <v>994</v>
       </c>
       <c r="J640" s="86" t="s">
         <v>970</v>
@@ -29489,7 +29486,7 @@
         <v>104.84</v>
       </c>
       <c r="Q640" s="62" t="s">
-        <v>994</v>
+        <v>992</v>
       </c>
     </row>
     <row r="641" spans="1:17" x14ac:dyDescent="0.55000000000000004">
@@ -29504,7 +29501,7 @@
         <v>737</v>
       </c>
       <c r="E641" s="91" t="s">
-        <v>980</v>
+        <v>979</v>
       </c>
       <c r="F641" s="89" t="s">
         <v>13</v>
@@ -29542,7 +29539,7 @@
         <v>738</v>
       </c>
       <c r="E642" s="91" t="s">
-        <v>980</v>
+        <v>979</v>
       </c>
       <c r="F642" s="89" t="s">
         <v>13</v>
@@ -29580,7 +29577,7 @@
         <v>862</v>
       </c>
       <c r="E643" s="91" t="s">
-        <v>980</v>
+        <v>979</v>
       </c>
       <c r="F643" s="89" t="s">
         <v>13</v>
@@ -29616,7 +29613,7 @@
         <v>863</v>
       </c>
       <c r="E644" s="91" t="s">
-        <v>980</v>
+        <v>979</v>
       </c>
       <c r="F644" s="89" t="s">
         <v>13</v>
@@ -29626,7 +29623,7 @@
       </c>
       <c r="H644" s="66"/>
       <c r="I644" s="86" t="s">
-        <v>995</v>
+        <v>994</v>
       </c>
       <c r="J644" s="86" t="s">
         <v>970</v>
@@ -29644,7 +29641,7 @@
         <v>21.61</v>
       </c>
       <c r="Q644" s="62" t="s">
-        <v>994</v>
+        <v>992</v>
       </c>
     </row>
     <row r="645" spans="1:17" x14ac:dyDescent="0.55000000000000004">
@@ -29659,7 +29656,7 @@
         <v>864</v>
       </c>
       <c r="E645" s="91" t="s">
-        <v>980</v>
+        <v>979</v>
       </c>
       <c r="F645" s="89" t="s">
         <v>13</v>
@@ -29697,7 +29694,7 @@
         <v>865</v>
       </c>
       <c r="E646" s="91" t="s">
-        <v>980</v>
+        <v>979</v>
       </c>
       <c r="F646" s="89" t="s">
         <v>13</v>
@@ -29707,7 +29704,7 @@
       </c>
       <c r="H646" s="66"/>
       <c r="I646" s="86" t="s">
-        <v>995</v>
+        <v>994</v>
       </c>
       <c r="J646" s="86" t="s">
         <v>970</v>
@@ -29725,7 +29722,7 @@
         <v>20.92</v>
       </c>
       <c r="Q646" s="62" t="s">
-        <v>994</v>
+        <v>992</v>
       </c>
     </row>
     <row r="647" spans="1:17" x14ac:dyDescent="0.55000000000000004">
@@ -29740,7 +29737,7 @@
         <v>739</v>
       </c>
       <c r="E647" s="91" t="s">
-        <v>980</v>
+        <v>979</v>
       </c>
       <c r="F647" s="89" t="s">
         <v>13</v>
@@ -29778,7 +29775,7 @@
         <v>740</v>
       </c>
       <c r="E648" s="91" t="s">
-        <v>980</v>
+        <v>979</v>
       </c>
       <c r="F648" s="89" t="s">
         <v>13</v>
@@ -29816,7 +29813,7 @@
         <v>867</v>
       </c>
       <c r="E649" s="91" t="s">
-        <v>980</v>
+        <v>979</v>
       </c>
       <c r="F649" s="89" t="s">
         <v>13</v>
@@ -29852,7 +29849,7 @@
         <v>868</v>
       </c>
       <c r="E650" s="91" t="s">
-        <v>980</v>
+        <v>979</v>
       </c>
       <c r="F650" s="89" t="s">
         <v>13</v>
@@ -29888,7 +29885,7 @@
         <v>869</v>
       </c>
       <c r="E651" s="91" t="s">
-        <v>980</v>
+        <v>979</v>
       </c>
       <c r="F651" s="89" t="s">
         <v>13</v>
@@ -29924,7 +29921,7 @@
         <v>870</v>
       </c>
       <c r="E652" s="91" t="s">
-        <v>980</v>
+        <v>979</v>
       </c>
       <c r="F652" s="89" t="s">
         <v>13</v>
@@ -29960,7 +29957,7 @@
         <v>741</v>
       </c>
       <c r="E653" s="91" t="s">
-        <v>980</v>
+        <v>979</v>
       </c>
       <c r="F653" s="89" t="s">
         <v>13</v>
@@ -29970,7 +29967,7 @@
       </c>
       <c r="H653" s="66"/>
       <c r="I653" s="86" t="s">
-        <v>974</v>
+        <v>995</v>
       </c>
       <c r="J653" s="86" t="s">
         <v>970</v>
@@ -29998,7 +29995,7 @@
         <v>269</v>
       </c>
       <c r="E654" s="91" t="s">
-        <v>980</v>
+        <v>979</v>
       </c>
       <c r="F654" s="89" t="s">
         <v>13</v>
@@ -30036,7 +30033,7 @@
         <v>742</v>
       </c>
       <c r="E655" s="91" t="s">
-        <v>980</v>
+        <v>979</v>
       </c>
       <c r="F655" s="89" t="s">
         <v>13</v>
@@ -30046,7 +30043,7 @@
       </c>
       <c r="H655" s="66"/>
       <c r="I655" s="86" t="s">
-        <v>995</v>
+        <v>994</v>
       </c>
       <c r="J655" s="86" t="s">
         <v>970</v>
@@ -30064,7 +30061,7 @@
         <v>41.77</v>
       </c>
       <c r="Q655" s="62" t="s">
-        <v>994</v>
+        <v>992</v>
       </c>
     </row>
     <row r="656" spans="1:17" x14ac:dyDescent="0.55000000000000004">
@@ -30079,7 +30076,7 @@
         <v>743</v>
       </c>
       <c r="E656" s="91" t="s">
-        <v>980</v>
+        <v>979</v>
       </c>
       <c r="F656" s="89" t="s">
         <v>13</v>
@@ -30089,7 +30086,7 @@
       </c>
       <c r="H656" s="66"/>
       <c r="I656" s="86" t="s">
-        <v>995</v>
+        <v>994</v>
       </c>
       <c r="J656" s="86" t="s">
         <v>970</v>
@@ -30107,13 +30104,13 @@
         <v>49.12</v>
       </c>
       <c r="Q656" s="62" t="s">
-        <v>994</v>
+        <v>992</v>
       </c>
     </row>
   </sheetData>
   <autoFilter ref="A1:Q656" xr:uid="{00000000-0001-0000-0000-000000000000}"/>
   <phoneticPr fontId="6" type="noConversion"/>
-  <dataValidations disablePrompts="1" count="1">
+  <dataValidations count="1">
     <dataValidation type="list" showInputMessage="1" showErrorMessage="1" sqref="H1:H53 H266:H1048576" xr:uid="{F2143DCB-C410-4A50-B8D0-CD2147393857}">
       <formula1>#REF!</formula1>
     </dataValidation>
@@ -30122,7 +30119,7 @@
   <pageSetup paperSize="8" scale="87" orientation="landscape" horizontalDpi="300" verticalDpi="300" r:id="rId1"/>
   <extLst>
     <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{CCE6A557-97BC-4b89-ADB6-D9C93CAAB3DF}">
-      <x14:dataValidations xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main" disablePrompts="1" count="1">
+      <x14:dataValidations xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main" count="1">
         <x14:dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" xr:uid="{46C7134D-9AD8-4B08-9FAD-20A7D7C8081D}">
           <x14:formula1>
             <xm:f>Hilfsliste!$A$2:$A$16</xm:f>
@@ -30142,7 +30139,7 @@
   <sheetData>
     <row r="1" spans="1:1" x14ac:dyDescent="0.75">
       <c r="A1" t="s">
-        <v>979</v>
+        <v>978</v>
       </c>
     </row>
     <row r="2" spans="1:1" x14ac:dyDescent="0.75">
@@ -30152,12 +30149,12 @@
     </row>
     <row r="3" spans="1:1" x14ac:dyDescent="0.75">
       <c r="A3" t="s">
-        <v>980</v>
+        <v>979</v>
       </c>
     </row>
     <row r="4" spans="1:1" x14ac:dyDescent="0.75">
       <c r="A4" t="s">
-        <v>981</v>
+        <v>980</v>
       </c>
     </row>
     <row r="5" spans="1:1" x14ac:dyDescent="0.75">
@@ -30167,42 +30164,42 @@
     </row>
     <row r="6" spans="1:1" x14ac:dyDescent="0.75">
       <c r="A6" t="s">
-        <v>989</v>
+        <v>988</v>
       </c>
     </row>
     <row r="7" spans="1:1" x14ac:dyDescent="0.75">
       <c r="A7" t="s">
-        <v>982</v>
+        <v>981</v>
       </c>
     </row>
     <row r="8" spans="1:1" x14ac:dyDescent="0.75">
       <c r="A8" t="s">
-        <v>983</v>
+        <v>982</v>
       </c>
     </row>
     <row r="9" spans="1:1" x14ac:dyDescent="0.75">
       <c r="A9" t="s">
-        <v>984</v>
+        <v>983</v>
       </c>
     </row>
     <row r="10" spans="1:1" x14ac:dyDescent="0.75">
       <c r="A10" t="s">
-        <v>985</v>
+        <v>984</v>
       </c>
     </row>
     <row r="11" spans="1:1" x14ac:dyDescent="0.75">
       <c r="A11" t="s">
-        <v>986</v>
+        <v>985</v>
       </c>
     </row>
     <row r="12" spans="1:1" x14ac:dyDescent="0.75">
       <c r="A12" t="s">
-        <v>987</v>
+        <v>986</v>
       </c>
     </row>
     <row r="13" spans="1:1" x14ac:dyDescent="0.75">
       <c r="A13" t="s">
-        <v>988</v>
+        <v>987</v>
       </c>
     </row>
     <row r="14" spans="1:1" x14ac:dyDescent="0.75">
@@ -30212,7 +30209,7 @@
     </row>
     <row r="15" spans="1:1" x14ac:dyDescent="0.75">
       <c r="A15" t="s">
-        <v>990</v>
+        <v>989</v>
       </c>
     </row>
   </sheetData>
@@ -40707,22 +40704,22 @@
   <sheetData>
     <row r="1" spans="1:1" x14ac:dyDescent="0.75">
       <c r="A1" t="s">
-        <v>975</v>
+        <v>974</v>
       </c>
     </row>
     <row r="3" spans="1:1" x14ac:dyDescent="0.75">
       <c r="A3" t="s">
-        <v>976</v>
+        <v>975</v>
       </c>
     </row>
     <row r="4" spans="1:1" x14ac:dyDescent="0.75">
       <c r="A4" t="s">
-        <v>977</v>
+        <v>976</v>
       </c>
     </row>
     <row r="5" spans="1:1" x14ac:dyDescent="0.75">
       <c r="A5" t="s">
-        <v>978</v>
+        <v>977</v>
       </c>
     </row>
   </sheetData>
